--- a/PPREstimation/output/top10/28_646_Guinea_(1998).xlsx
+++ b/PPREstimation/output/top10/28_646_Guinea_(1998).xlsx
@@ -701,7 +701,11 @@
           <t>DET</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Detritus; nonliving organic material.</t>
+        </is>
+      </c>
       <c r="F3" s="2" t="n">
         <v>1</v>
       </c>
@@ -785,7 +789,11 @@
           <t>PP</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Phytoplankton primary producers; source p.125 explicitly says information on aquatic plants was unavailable.</t>
+        </is>
+      </c>
       <c r="F4" s="2" t="n">
         <v>1</v>
       </c>
@@ -869,7 +877,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Herbivorous zooplankton: copepods, cladocerans, invertebrate larvae and unidentified organisms as classified by source p.125.</t>
+        </is>
+      </c>
       <c r="F5" s="2" t="n">
         <v>2</v>
       </c>
@@ -953,7 +965,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Carnivorous zooplankton: euphausiids, appendicularians and chaetognaths as classified by the source p.125; preserve the author's grouping.</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="n">
         <v>2.816326530612245</v>
       </c>
@@ -1037,7 +1053,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Macrobenthic bivalves, other molluscs, polychaetes, echinoderms and crustaceans other than those in Crustacés (source p.126).</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="n">
         <v>2.173469387755102</v>
       </c>
@@ -1121,7 +1141,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Commercial and noncommercial lobsters, shrimp and crabs (source p.125).</t>
+        </is>
+      </c>
       <c r="F8" s="2" t="n">
         <v>2.966702470461869</v>
       </c>
@@ -1205,7 +1229,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Commercial and noncommercial octopus, cuttlefish and squid; catches dominated by Sepia spp. (source p.125).</t>
+        </is>
+      </c>
       <c r="F9" s="2" t="n">
         <v>3.992010945734135</v>
       </c>
@@ -1289,7 +1317,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Myctophidae divers; Benthosema glaciale; Cyclothone spp; Diaphus spp (Table 6 p.131; printed names; full accepted-name crosswalk in members.csv).</t>
+        </is>
+      </c>
       <c r="F10" s="2" t="n">
         <v>3.231486703099204</v>
       </c>
@@ -1373,7 +1405,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Ariomma melanum; Bathygadus melanobranchus; Bathymicrops regis; Bathypterois spp; Diretmichthys parini; Nezumia spp; Scopelosaurus lepidus; Serrivomer spp; Stomias longibarbatus; Trigla lyra (Table 6 p.131; printed names; full accepted-name crosswalk in members.csv).</t>
+        </is>
+      </c>
       <c r="F11" s="2" t="n">
         <v>3.556769495654368</v>
       </c>
@@ -1457,7 +1493,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aristostomias xenostoma; Astronesthes spp; Chauliodus schmidti; Eustomias spp; Sternoptyx spp; Stomias affinis; Stomias lampropeltis (Table 6 p.131; printed names; full accepted-name crosswalk in members.csv).</t>
+        </is>
+      </c>
       <c r="F12" s="2" t="n">
         <v>3.754116066357739</v>
       </c>
@@ -1541,7 +1581,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Alepocephalus rostratus; Bathysaurus ferox; Epigonus telescopus; Gempylus serpens; Helicolenus dactylopterus dactylopterus; Hoplostethus mediterraneus; Lepidocybium flavobrunneum; Lophius vaillanti; Nemichthys scolopaceus; Polyprion americanus; Pontinus kuhlii (Table 6 p.131; printed names; full accepted-name crosswalk in members.csv).</t>
+        </is>
+      </c>
       <c r="F13" s="2" t="n">
         <v>4.096801257197423</v>
       </c>
@@ -1625,7 +1669,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Antigonia capros; Ariomma bondi; Chilomycterus spinosus; Chromis cadenati; Sargocentron hastatus; Sphoeroides spengleri; Stephanolepis hispidus; Syacium micrurum; Synchiropus phaeton (Table 6 p.131; printed names; full accepted-name crosswalk in members.csv).</t>
+        </is>
+      </c>
       <c r="F14" s="2" t="n">
         <v>3.173469387755102</v>
       </c>
@@ -1709,7 +1757,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Antennarius pardalis; Apogon imberbis; Arnoglossus imperialis; Bembrops heterurus; Chlorophthalmus agassizi; Pontinus accraensis; Solitas gruveli; Uranoscopus polli (Table 6 p.131; printed names; full accepted-name crosswalk in members.csv).</t>
+        </is>
+      </c>
       <c r="F15" s="2" t="n">
         <v>3.811781670790351</v>
       </c>
@@ -1793,7 +1845,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Mugil curema; Balistes carolinensis; Balistes punctatus; Balistes vetula; Boops boops; Chelidonichthys gabonensis; Chelidonichthys lastoviza; Pagellus bellottii; Plectorhinchus mediterraneus; Pseudupeneus prayensis; Scarus hoefleri; Xyrichtys novacula (Table 6 p.131; printed names; full accepted-name crosswalk in members.csv).</t>
+        </is>
+      </c>
       <c r="F16" s="2" t="n">
         <v>3.261758427043216</v>
       </c>
@@ -1877,7 +1933,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aulopus cadenati; Chelidonichthys lucerna; Dentex macrophthalmus; Dentex maroccanus; Lophiodes kempi; Priacanthus arenatus; Rypticus saponaceus; Scorpaena elongata; Serranus cabrilla; Sphoeroides pachygaster; Trachinocephalus myops; Trachinus armatus; Zenopsis conchifer (Table 6 p.131; printed names; full accepted-name crosswalk in members.csv).</t>
+        </is>
+      </c>
       <c r="F17" s="2" t="n">
         <v>3.980685424383546</v>
       </c>
@@ -1961,7 +2021,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Dactylopterus volitans; Echeneis naucrates; Sparus auratus; Umbrina canariensis (Table 6 p.131; printed names; full accepted-name crosswalk in members.csv).</t>
+        </is>
+      </c>
       <c r="F18" s="2" t="n">
         <v>3.13172663802363</v>
       </c>
@@ -2045,7 +2109,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Cephalopholis taeniops; Epinephelus aeneus; Epinephelus fasciatus; Epinephelus goreensis; Epinephelus caninus; Epinephelus marginatus; Merluccius polli; Merluccius senegalensis; Pagrus caeruleostictus; Pagrus pagrus; Solitas gruveli; Umbrina ronchus; Zeus faber; Congridae (Table 6 p.131; printed names; full accepted-name crosswalk in members.csv).</t>
+        </is>
+      </c>
       <c r="F19" s="2" t="n">
         <v>3.890047535908185</v>
       </c>
@@ -2129,7 +2197,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Abudefduf saxatilis; Brachydeuterus auritus; Dicologlossa cuneata; Oblada melanura; Chromis chromis; Gerres nigri; Labrisomus nuchipinnis; Pegusa spp; Trachinus spp (Table 6 p.131; printed names; full accepted-name crosswalk in members.csv).</t>
+        </is>
+      </c>
       <c r="F20" s="2" t="n">
         <v>2.92177279738255</v>
       </c>
@@ -2213,7 +2285,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Pentanemus quinquarius (Table 6 p.131; printed names; full accepted-name crosswalk in members.csv).</t>
+        </is>
+      </c>
       <c r="F21" s="2" t="n">
         <v>3.874411605399239</v>
       </c>
@@ -2297,7 +2373,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Citharus linguatula; Eucinostomus melanopterus; Monodactylus sebae; Pteroscion peli; Stromateus fiatola; Scorpaenoidae (Table 6 p.131; printed names; full accepted-name crosswalk in members.csv).</t>
+        </is>
+      </c>
       <c r="F22" s="2" t="n">
         <v>3.775374841579309</v>
       </c>
@@ -2381,7 +2461,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Bothus podas; Cynoglossus canariensis; Cynoglossus monodi; Cynoglossus senegalensis; Dicologlossa hexophthalma; Diodon hystrix; Diplodus puntazzo; Lethrinus atlanticus; Plectorhinchus macrolepis; Pomadasys incisus; Pomadasys jubelini; Pomadasys perotaei; Pomadasys rogerii (Table 6 p.131; printed names; full accepted-name crosswalk in members.csv).</t>
+        </is>
+      </c>
       <c r="F23" s="2" t="n">
         <v>3.259920039568824</v>
       </c>
@@ -2465,7 +2549,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Galeoides decadactylus (Table 6 p.131; printed names; full accepted-name crosswalk in members.csv).</t>
+        </is>
+      </c>
       <c r="F24" s="2" t="n">
         <v>3.817576962206467</v>
       </c>
@@ -2549,7 +2637,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Acanthurus monroviae; Aluterus schoepfii; Liza dumerili; Liza falcipinnis; Liza grandisquamis; Mugil bananensis; Sarpa salpa (Table 6 p.131; printed names; full accepted-name crosswalk in members.csv).</t>
+        </is>
+      </c>
       <c r="F25" s="2" t="n">
         <v>2.319780433270403</v>
       </c>
@@ -2633,7 +2725,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Ephippus goreensis; Chaetodipterus lippei; Drepane africana (Table 6 p.131; printed names; full accepted-name crosswalk in members.csv).</t>
+        </is>
+      </c>
       <c r="F26" s="2" t="n">
         <v>3.346107613991568</v>
       </c>
@@ -2717,7 +2813,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Arius gigas; Arius heudelotii; Arius latiscutatus; Arius parkii (Table 6 p.131; printed names; full accepted-name crosswalk in members.csv).</t>
+        </is>
+      </c>
       <c r="F27" s="2" t="n">
         <v>3.692104906408646</v>
       </c>
@@ -2801,7 +2901,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Batrachoides liberiensis; Bodianus speciosus; Gymnothorax mareei; Halobatrachus didactylus; Holacanthus africanus; Naucrates ductor (Table 6 p.131; printed names; full accepted-name crosswalk in members.csv).</t>
+        </is>
+      </c>
       <c r="F28" s="2" t="n">
         <v>3.602368243537031</v>
       </c>
@@ -2885,7 +2989,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Ephippion guttifer; Argyrosomus regius; Cynoponticus ferox; Dentex canariensis; Dentex gibbosus; Epinephelus costae; Epinephelus itajara; Fistularia petimba; Fistularia tabacaria; Lobotes surinamensis; Lutjanus agennes; Lutjanus endecacanthus; Lutjanus fulgens; Lutjanus goreensis; Muraena melanotis; Muraena robusta; Psettodes belcheri; Trichiurus lepturus (Table 6 p.131; printed names; full accepted-name crosswalk in members.csv).</t>
+        </is>
+      </c>
       <c r="F29" s="2" t="n">
         <v>3.980354589606851</v>
       </c>
@@ -2969,7 +3077,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Polydactylus quadrifilis (Table 6 p.131; printed names; full accepted-name crosswalk in members.csv).</t>
+        </is>
+      </c>
       <c r="F30" s="2" t="n">
         <v>4.074343561818063</v>
       </c>
@@ -3053,7 +3165,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Pseudotolithus senegalensis; Pseudotolithus senegallus; Pseudotolithus typus; Pseudotolithus elongatus; Pseudotolithus epipercus; Pseudotolithus moorii (Table 6 p.131; printed names; full accepted-name crosswalk in members.csv).</t>
+        </is>
+      </c>
       <c r="F31" s="2" t="n">
         <v>3.955340789905125</v>
       </c>
@@ -3137,7 +3253,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Cheilopogon cyanopterus; Cheilopogon nigricans; Decapterus punctatus; Scomber japonicus; Selar crumenophthalmus; Trachurus capensis; Trachurus trecae (Table 6 p.131; printed names; full accepted-name crosswalk in members.csv).</t>
+        </is>
+      </c>
       <c r="F32" s="2" t="n">
         <v>3.213549764705561</v>
       </c>
@@ -3221,7 +3341,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Ablennes hians; Alectis ciliaris; Coryphaena equiselis; Coryphaena hippurus; Megalops atlanticus; Mola mola (Table 6 p.131; printed names; full accepted-name crosswalk in members.csv).</t>
+        </is>
+      </c>
       <c r="F33" s="2" t="n">
         <v>4.100191369575258</v>
       </c>
@@ -3305,7 +3429,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Ethmalosa fimbriata (Table 6 p.131; printed names; full accepted-name crosswalk in members.csv).</t>
+        </is>
+      </c>
       <c r="F34" s="2" t="n">
         <v>2.517346938775511</v>
       </c>
@@ -3389,7 +3517,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Engraulis encrasicolus; Hemiramphus brasiliensis; Ilisha africana; Sardinella aurita; Sardinella maderensis (Table 6 p.131; printed names; full accepted-name crosswalk in members.csv).</t>
+        </is>
+      </c>
       <c r="F35" s="2" t="n">
         <v>2.851867999236284</v>
       </c>
@@ -3473,7 +3605,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Albula vulpes; Alectis alexandrinus; Caranx crysos; Caranx hippos; Caranx rhonchus; Caranx senegallus; Chloroscombrus chrysurus; Elops lacerta; Elops senegalensis; Hemicaranx bicolor; Lichia amia; Pomatomus saltatrix; Rachycentron canadum; Selene dorsalis; Seriola dumerili; Sphyraena afra; Sphyraena guachancho; Sphyraena sphyraena; Trachinotus goreensis; Trachinotus maxillosus (Table 6 p.131; printed names; full accepted-name crosswalk in members.csv).</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="n">
         <v>4.070766630902783</v>
       </c>
@@ -3557,7 +3693,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Orcynopsis unicolor; Scomberomorus tritor; Acanthocybium solandri; Auxis rochei; Euthynnus alletteratus; Auxis thazard; Sarda sarda (Table 6 p.131; printed names; full accepted-name crosswalk in members.csv).</t>
+        </is>
+      </c>
       <c r="F37" s="2" t="n">
         <v>4.181473980164887</v>
       </c>
@@ -3641,7 +3781,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Istiophorus albicans; Katsuwonus pelamis; Makaira indica; Makaira nigricans; Tetrapturus albidus; Thunnus alalunga; Thunnus albacares; Thunnus obesus; Xiphias gladius (Table 6 p.131; printed names; full accepted-name crosswalk in members.csv).</t>
+        </is>
+      </c>
       <c r="F38" s="2" t="n">
         <v>4.477694868523266</v>
       </c>
@@ -3725,7 +3869,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Dasyatis pastinaca; Mobula rochebrunei; Rhinobatos albomaculatus; Torpedo torpedo (Table 6 p.131; printed names; full accepted-name crosswalk in members.csv).</t>
+        </is>
+      </c>
       <c r="F39" s="2" t="n">
         <v>4.117796713578526</v>
       </c>
@@ -3809,7 +3957,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Dipturus doutrei; Etmopterus polli; Galeus polli; Raja maderensis; Raja miraletus; Rajella bigelowi; Squalus megalops (Table 6 p.131; printed names; full accepted-name crosswalk in members.csv).</t>
+        </is>
+      </c>
       <c r="F40" s="2" t="n">
         <v>4.485871887330383</v>
       </c>
@@ -3893,7 +4045,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Alopias vulpinus; Carcharhinus limbatus; Dasyatis centroura; Dasyatis margarita; Galeocerdo cuvier; Gymnura. micrura; Leptocharias smithii; Mustelus mustelus; Pteromylaeus bovinus; Rhinobatos rhinobatos; Rhinoptera bonasus; Rhinoptera marginata; Rhizoprionodon acutus; Rhynchobatus luebberti; Squatina oculata; Torpedo marmorata; Zanobatus schoenleinii (Table 6 p.131; printed names; full accepted-name crosswalk in members.csv).</t>
+        </is>
+      </c>
       <c r="F41" s="2" t="n">
         <v>4.122550944059172</v>
       </c>
@@ -3977,7 +4133,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Bathyraja hesperafricana; Carcharhinus altimus; Carcharhinus longimanus; Isurus oxyrhinchus; Leucoraja leucosticta; Prionace glauca; Raja clavata; Rhincodon typus; Sphyrna zygaena; Squalus acanthia; Squalus blainville; Squatina aculeata; Torpedo nobiliana (Table 6 p.131; printed names; full accepted-name crosswalk in members.csv).</t>
+        </is>
+      </c>
       <c r="F42" s="2" t="n">
         <v>4.545730475051753</v>
       </c>
@@ -4061,7 +4221,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Ardea cinerea; Ardea goliath; Ardeola ralloides; Butorides striatus; Ciconia episcopus; Egretta alba; Egretta garzetta; Egretta gularis; Egretta intermedia; Mycteria ibis; Platalea alba; Scopus umbretta; Threskiornis aethiopica; Chlidonias laucopterus; Chlidonias niger; Gelochelidon nilotica; Larus cirrocephalus; Larus fuscus; Larus genei; Larus ridibundus; Rynchops flavirostris; Sterna bengalensis; Sterna caspia; Sterna hirundo; Sterna maxima; Sterna sandvicensis; Steruna albifrons; Actitits hypoleucos; Arenaria interpres; Burhinus senegalensis; Calidris alba; Calidris alpina; Calidris canutus; Calidris ferruginea; Calidris minuta; Charadrius alexandrinus; Charadrius hiaticula; Charadrius marginatus; Charadrius pecuarius; Glareola pratincola; Haematopus ostralegus; Himantopus himantopus; Limosa lapponica; Limosa limosa; Numenius arquata; Numenius phaeopus; Pluvialis squatarola; Recurvirostra avostta; Tringa erythropus; Tringa nebularia; Tringa stagnatilis; Tringa totanus; Vanellus spinosus; Alcedo cristata; Anhinga anhinga; Ceryle rudis; Megaceryle maxima; Pelecanus rufescens; Halcyon leucocephola; Pelecanus onocrotalus; Phalacrocorax africanus; Phoenicopterus minor; Phoenicopterus ruber (shore/coastal bird inventory, Table 4 pp.129-130; printed spellings; includes census taxa, with resident time weighted by source).</t>
+        </is>
+      </c>
       <c r="F43" s="2" t="n">
         <v>3.545462130271481</v>
       </c>
@@ -4145,7 +4309,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Caretta caretta. Source p.127 states that this turtle represents the modeled marine-turtle group, although four other sea-turtle species are present regionally.</t>
+        </is>
+      </c>
       <c r="F44" s="2" t="n">
         <v>2.181632653061225</v>
       </c>
@@ -4229,7 +4397,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Physeter macrocephalus; Globicephala melas; Globicephala macrorhynchus; Delphinus delphi; Stenella coeruleoalba; Ziphius cavirostris; Stenella attenuata; Hyperoodon ampullatus; Grampeus griseus; Tursiops truncatus; Phocaena phocoena; Pseudorca crassidens; Orcinus orca (Table 2 p.126; printed spellings, composition adopted by source).</t>
+        </is>
+      </c>
       <c r="F45" s="2" t="n">
         <v>4.717188474794793</v>
       </c>
@@ -4313,7 +4485,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Balaenoptera acurostrata; Balaenoptera edeni; Balaenoptera borealis; Balaenoptera musculus; Megaptera novaeangliae; Balaenoptera physalus (Table 2 p.126; printed spellings, Moroccan analogue composition adopted by the source).</t>
+        </is>
+      </c>
       <c r="F46" s="2" t="n">
         <v>3.979562356563989</v>
       </c>
@@ -4772,10 +4948,10 @@
         <v>2.7</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>4.602694481129704</v>
+        <v>4.597262806651633</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>7.554532001682648</v>
+        <v>7.505630400226367</v>
       </c>
     </row>
     <row r="6">
@@ -4836,10 +5012,10 @@
         <v>9.591304347826091</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>20.67320000872544</v>
+        <v>20.58642319289632</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>43.74174084169443</v>
+        <v>42.83231604378508</v>
       </c>
     </row>
     <row r="7">
@@ -4900,10 +5076,10 @@
         <v>6.21428571428571</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>14.05456833214566</v>
+        <v>14.06964581018163</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>37.28773094373179</v>
+        <v>35.95337081765199</v>
       </c>
     </row>
     <row r="8">
@@ -4964,10 +5140,10 @@
         <v>14.7617814193207</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>42.99447989915794</v>
+        <v>43.38739827845263</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>111.4975676691513</v>
+        <v>109.873168166362</v>
       </c>
     </row>
     <row r="9">
@@ -5028,10 +5204,10 @@
         <v>71.4717996231623</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>279.060052025653</v>
+        <v>275.4013387269482</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>1055.287691449896</v>
+        <v>1017.651066096116</v>
       </c>
     </row>
     <row r="10">
@@ -5092,10 +5268,10 @@
         <v>14.7847937303281</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>41.84265576516914</v>
+        <v>40.65122163500696</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>326.0557298755097</v>
+        <v>318.2118543021983</v>
       </c>
     </row>
     <row r="11">
@@ -5156,10 +5332,10 @@
         <v>89.79642604263439</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>278.1177228566078</v>
+        <v>273.4791901578748</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>1000.950147465697</v>
+        <v>990.3410206887481</v>
       </c>
     </row>
     <row r="12">
@@ -5220,10 +5396,10 @@
         <v>73.4084435973388</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>250.8419870815471</v>
+        <v>247.8993849996301</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>1280.078757754702</v>
+        <v>1250.020162688867</v>
       </c>
     </row>
     <row r="13">
@@ -5284,10 +5460,10 @@
         <v>236.286264691325</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>1096.347139786239</v>
+        <v>1084.214762662649</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>4534.882798247629</v>
+        <v>4425.550085170168</v>
       </c>
     </row>
     <row r="14">
@@ -5348,10 +5524,10 @@
         <v>43.6172506738544</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>124.9732796923049</v>
+        <v>124.6160948807996</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>348.5613794090116</v>
+        <v>336.0173740224187</v>
       </c>
     </row>
     <row r="15">
@@ -5412,10 +5588,10 @@
         <v>145.634911123825</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>585.5158095936424</v>
+        <v>572.3319480325749</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>2061.542415910371</v>
+        <v>1986.22292772838</v>
       </c>
     </row>
     <row r="16">
@@ -5476,10 +5652,10 @@
         <v>88.6832945479654</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>273.7400197959449</v>
+        <v>274.7435064906737</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>747.5493473736694</v>
+        <v>730.0932695810826</v>
       </c>
     </row>
     <row r="17">
@@ -5540,10 +5716,10 @@
         <v>230.471022450333</v>
       </c>
       <c r="U17" s="2" t="n">
-        <v>944.7116688760319</v>
+        <v>931.6823239373899</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>3116.422635942231</v>
+        <v>2978.125002299211</v>
       </c>
     </row>
     <row r="18">
@@ -5604,10 +5780,10 @@
         <v>45.2418155333481</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>146.4767821314352</v>
+        <v>149.956524527334</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>399.1929132298223</v>
+        <v>395.1192515551665</v>
       </c>
     </row>
     <row r="19">
@@ -5668,10 +5844,10 @@
         <v>502.733116359586</v>
       </c>
       <c r="U19" s="2" t="n">
-        <v>2405.309691624939</v>
+        <v>2393.190154238761</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>9815.891039409002</v>
+        <v>9644.194140463422</v>
       </c>
     </row>
     <row r="20">
@@ -5732,10 +5908,10 @@
         <v>32.1382373254986</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>96.84286809235442</v>
+        <v>96.99122095818534</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>256.4618059363722</v>
+        <v>248.3211962608204</v>
       </c>
     </row>
     <row r="21">
@@ -5796,10 +5972,10 @@
         <v>40389.8015747168</v>
       </c>
       <c r="U21" s="2" t="n">
-        <v>455.6153404269531</v>
+        <v>460.525660737567</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>1244.121946941878</v>
+        <v>1212.163930138708</v>
       </c>
     </row>
     <row r="22">
@@ -5860,10 +6036,10 @@
         <v>113.683416618975</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>459.4409725758825</v>
+        <v>461.5375767460991</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>1615.716455306842</v>
+        <v>1572.808567304289</v>
       </c>
     </row>
     <row r="23">
@@ -5924,10 +6100,10 @@
         <v>43.2021936037326</v>
       </c>
       <c r="U23" s="2" t="n">
-        <v>136.3435430434293</v>
+        <v>135.8414053656921</v>
       </c>
       <c r="V23" s="2" t="n">
-        <v>347.7567022913382</v>
+        <v>344.6650991948791</v>
       </c>
     </row>
     <row r="24">
@@ -5988,10 +6164,10 @@
         <v>86.7602116035718</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>308.8715089278272</v>
+        <v>314.7816235101479</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>878.6139232489521</v>
+        <v>840.2198830872899</v>
       </c>
     </row>
     <row r="25">
@@ -6052,10 +6228,10 @@
         <v>18.1462029026673</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>41.26208326273742</v>
+        <v>40.73217786126737</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>83.32853810465024</v>
+        <v>82.33755050988032</v>
       </c>
     </row>
     <row r="26">
@@ -6116,10 +6292,10 @@
         <v>91.2060999390233</v>
       </c>
       <c r="U26" s="2" t="n">
-        <v>294.2779889336226</v>
+        <v>298.0924558190391</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>840.8172923107722</v>
+        <v>817.7492438310887</v>
       </c>
     </row>
     <row r="27">
@@ -6180,10 +6356,10 @@
         <v>12817.2794152048</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>507.0345975412874</v>
+        <v>506.2071334045904</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>1410.168736381215</v>
+        <v>1370.742426914867</v>
       </c>
     </row>
     <row r="28">
@@ -6244,10 +6420,10 @@
         <v>28917.6375575529</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>1641.958379238651</v>
+        <v>1628.194695707954</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>4944.531661873421</v>
+        <v>4781.767213139441</v>
       </c>
     </row>
     <row r="29">
@@ -6308,10 +6484,10 @@
         <v>13815.1671528612</v>
       </c>
       <c r="U29" s="2" t="n">
-        <v>2716.21821838225</v>
+        <v>2674.282782669413</v>
       </c>
       <c r="V29" s="2" t="n">
-        <v>17952.9926576431</v>
+        <v>16812.29830107797</v>
       </c>
     </row>
     <row r="30">
@@ -6372,10 +6548,10 @@
         <v>44887.4138218465</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>1376.217792022098</v>
+        <v>1356.920837413488</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>3923.202485697203</v>
+        <v>3943.075354225288</v>
       </c>
     </row>
     <row r="31">
@@ -6436,10 +6612,10 @@
         <v>3691.5440627593</v>
       </c>
       <c r="U31" s="2" t="n">
-        <v>734.4159328423056</v>
+        <v>736.9540910241141</v>
       </c>
       <c r="V31" s="2" t="n">
-        <v>2533.531988521782</v>
+        <v>2463.064614465615</v>
       </c>
     </row>
     <row r="32">
@@ -6500,10 +6676,10 @@
         <v>25.5305680604518</v>
       </c>
       <c r="U32" s="2" t="n">
-        <v>73.9775883880984</v>
+        <v>71.89501656701381</v>
       </c>
       <c r="V32" s="2" t="n">
-        <v>294.7008639799253</v>
+        <v>297.1981429492287</v>
       </c>
     </row>
     <row r="33">
@@ -6564,10 +6740,10 @@
         <v>4998.0851957047</v>
       </c>
       <c r="U33" s="2" t="n">
-        <v>1353.985365116356</v>
+        <v>1354.49571621576</v>
       </c>
       <c r="V33" s="2" t="n">
-        <v>5057.082631658946</v>
+        <v>5057.925718751013</v>
       </c>
     </row>
     <row r="34">
@@ -6628,10 +6804,10 @@
         <v>18.4442170542495</v>
       </c>
       <c r="U34" s="2" t="n">
-        <v>40.01998888020917</v>
+        <v>39.20415535765962</v>
       </c>
       <c r="V34" s="2" t="n">
-        <v>80.14592380350645</v>
+        <v>80.23133492244214</v>
       </c>
     </row>
     <row r="35">
@@ -6692,10 +6868,10 @@
         <v>20.5476567041468</v>
       </c>
       <c r="U35" s="2" t="n">
-        <v>61.97234884916978</v>
+        <v>61.34077720998902</v>
       </c>
       <c r="V35" s="2" t="n">
-        <v>165.700465385664</v>
+        <v>159.5096477892282</v>
       </c>
     </row>
     <row r="36">
@@ -6756,10 +6932,10 @@
         <v>8846.789624593221</v>
       </c>
       <c r="U36" s="2" t="n">
-        <v>2667.708495623913</v>
+        <v>2645.523944103685</v>
       </c>
       <c r="V36" s="2" t="n">
-        <v>13019.89350755795</v>
+        <v>12354.97382371667</v>
       </c>
     </row>
     <row r="37">
@@ -6820,10 +6996,10 @@
         <v>149.418325632159</v>
       </c>
       <c r="U37" s="2" t="n">
-        <v>638.3179656925651</v>
+        <v>633.0552076156656</v>
       </c>
       <c r="V37" s="2" t="n">
-        <v>3921.893127505595</v>
+        <v>3726.667281850449</v>
       </c>
     </row>
     <row r="38">
@@ -6884,10 +7060,10 @@
         <v>2167.37954123905</v>
       </c>
       <c r="U38" s="2" t="n">
-        <v>1629.158356786491</v>
+        <v>1598.647747101092</v>
       </c>
       <c r="V38" s="2" t="n">
-        <v>12090.18358250759</v>
+        <v>12125.41410542123</v>
       </c>
     </row>
     <row r="39">
@@ -6948,10 +7124,10 @@
         <v>8068.60412282659</v>
       </c>
       <c r="U39" s="2" t="n">
-        <v>3243.913864360747</v>
+        <v>3191.027676244393</v>
       </c>
       <c r="V39" s="2" t="n">
-        <v>24712.49409565554</v>
+        <v>24373.86353893469</v>
       </c>
     </row>
     <row r="40">
@@ -7012,10 +7188,10 @@
         <v>1087.06724707881</v>
       </c>
       <c r="U40" s="2" t="n">
-        <v>5060.985744073381</v>
+        <v>5187.892057964855</v>
       </c>
       <c r="V40" s="2" t="n">
-        <v>38638.87290551296</v>
+        <v>38259.64232862164</v>
       </c>
     </row>
     <row r="41">
@@ -7076,10 +7252,10 @@
         <v>22930.4238983143</v>
       </c>
       <c r="U41" s="2" t="n">
-        <v>12066.59429853709</v>
+        <v>12078.75140268669</v>
       </c>
       <c r="V41" s="2" t="n">
-        <v>139716.4700880515</v>
+        <v>133154.3696116995</v>
       </c>
     </row>
     <row r="42">
@@ -7140,10 +7316,10 @@
         <v>31482.8007124961</v>
       </c>
       <c r="U42" s="2" t="n">
-        <v>22932.2016381145</v>
+        <v>23157.18568296244</v>
       </c>
       <c r="V42" s="2" t="n">
-        <v>671240.2320720728</v>
+        <v>623084.0588927014</v>
       </c>
     </row>
     <row r="43">
@@ -7204,10 +7380,10 @@
         <v>36768.6104158684</v>
       </c>
       <c r="U43" s="2" t="n">
-        <v>29801.33396698616</v>
+        <v>29529.39555059259</v>
       </c>
       <c r="V43" s="2" t="n">
-        <v>315814.7293716724</v>
+        <v>301620.6787919171</v>
       </c>
     </row>
     <row r="44">
@@ -7268,10 +7444,10 @@
         <v>34.7037681159727</v>
       </c>
       <c r="U44" s="2" t="n">
-        <v>70.45278435616645</v>
+        <v>70.37633457884871</v>
       </c>
       <c r="V44" s="2" t="n">
-        <v>245.626779826916</v>
+        <v>243.2657790223243</v>
       </c>
     </row>
     <row r="45">
@@ -7332,10 +7508,10 @@
         <v>49147.8322414615</v>
       </c>
       <c r="U45" s="2" t="n">
-        <v>45845.83003431372</v>
+        <v>45081.64537338285</v>
       </c>
       <c r="V45" s="2" t="n">
-        <v>472174.6585205199</v>
+        <v>456953.901971593</v>
       </c>
     </row>
     <row r="46">
@@ -7396,10 +7572,10 @@
         <v>57370.4760913705</v>
       </c>
       <c r="U46" s="2" t="n">
-        <v>31965.02245855528</v>
+        <v>31616.12220711319</v>
       </c>
       <c r="V46" s="2" t="n">
-        <v>248550.3983338619</v>
+        <v>242908.6687601026</v>
       </c>
     </row>
   </sheetData>
@@ -7680,7 +7856,7 @@
         <v>-32.12008939505308</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>1.885526763619611</v>
+        <v>1.878087883662399</v>
       </c>
       <c r="V3" s="2" t="n">
         <v>0.4259477184223214</v>
@@ -7820,10 +7996,10 @@
         <v>-6.936026818515923</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>5.573258916817597</v>
+        <v>5.564543770877899</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>7.912069298334329</v>
+        <v>7.860853305148327</v>
       </c>
     </row>
     <row r="6">
@@ -7890,10 +8066,10 @@
         <v>-37.05265155629453</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>26.00759147380568</v>
+        <v>25.85536647293242</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>46.08849811427029</v>
+        <v>45.1319016450555</v>
       </c>
     </row>
     <row r="7">
@@ -7960,10 +8136,10 @@
         <v>-381.5210791259988</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>46.78419474590279</v>
+        <v>46.81788282657553</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>49.9240741166841</v>
+        <v>48.19726778794774</v>
       </c>
     </row>
     <row r="8">
@@ -8030,10 +8206,10 @@
         <v>-691.7086970186991</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>122.2161732212628</v>
+        <v>122.9263253691878</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>142.875060451637</v>
+        <v>140.8975049144198</v>
       </c>
     </row>
     <row r="9">
@@ -8100,10 +8276,10 @@
         <v>-2693.78971044137</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>704.2152756566685</v>
+        <v>696.0734625836174</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>1292.344587433423</v>
+        <v>1245.599369298057</v>
       </c>
     </row>
     <row r="10">
@@ -8170,10 +8346,10 @@
         <v>-294.0652519852261</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>81.5606660164726</v>
+        <v>78.98787536478874</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>381.654957016193</v>
+        <v>372.1769891195785</v>
       </c>
     </row>
     <row r="11">
@@ -8240,10 +8416,10 @@
         <v>-2740.125080224454</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>635.4476856765211</v>
+        <v>625.1285403218787</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>1200.924953056779</v>
+        <v>1187.940332262086</v>
       </c>
     </row>
     <row r="12">
@@ -8310,10 +8486,10 @@
         <v>-1962.48249564027</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>544.5351851874881</v>
+        <v>538.0634576558791</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>1516.750702384065</v>
+        <v>1480.144923443977</v>
       </c>
     </row>
     <row r="13">
@@ -8380,10 +8556,10 @@
         <v>-8011.455305706264</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>2682.644718169137</v>
+        <v>2656.811607945523</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>5517.173419137696</v>
+        <v>5385.068956264562</v>
       </c>
     </row>
     <row r="14">
@@ -8450,10 +8626,10 @@
         <v>-2677.846064808891</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>416.4953224849871</v>
+        <v>415.453035315079</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>466.6458401192457</v>
+        <v>450.3766805784952</v>
       </c>
     </row>
     <row r="15">
@@ -8520,10 +8696,10 @@
         <v>-6299.237463071768</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>1578.463796880351</v>
+        <v>1546.303441830053</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>2565.692755976544</v>
+        <v>2470.626866590555</v>
       </c>
     </row>
     <row r="16">
@@ -8590,10 +8766,10 @@
         <v>-4414.739473613688</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>804.3061887645554</v>
+        <v>805.7689636070436</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>967.6178850340229</v>
+        <v>945.5745855891123</v>
       </c>
     </row>
     <row r="17">
@@ -8660,10 +8836,10 @@
         <v>-10411.68983398419</v>
       </c>
       <c r="U17" s="2" t="n">
-        <v>2610.205618928899</v>
+        <v>2575.180215224021</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>3926.140840267151</v>
+        <v>3752.0189694639</v>
       </c>
     </row>
     <row r="18">
@@ -8730,10 +8906,10 @@
         <v>-2227.375206310696</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>427.8088859179441</v>
+        <v>437.215420181951</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>516.4626068550535</v>
+        <v>511.2901281751808</v>
       </c>
     </row>
     <row r="19">
@@ -8800,10 +8976,10 @@
         <v>-21764.35897890091</v>
       </c>
       <c r="U19" s="2" t="n">
-        <v>6531.343468311494</v>
+        <v>6493.939199569654</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>12271.70097950027</v>
+        <v>12062.96911240619</v>
       </c>
     </row>
     <row r="20">
@@ -8870,10 +9046,10 @@
         <v>-1347.823620351089</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>266.3786177621238</v>
+        <v>265.9906478294968</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>326.8691487450449</v>
+        <v>316.4557728011578</v>
       </c>
     </row>
     <row r="21">
@@ -8940,10 +9116,10 @@
         <v>-1079438.767153322</v>
       </c>
       <c r="U21" s="2" t="n">
-        <v>1188.149673812792</v>
+        <v>1199.76631783077</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>1564.314637901751</v>
+        <v>1524.660266415124</v>
       </c>
     </row>
     <row r="22">
@@ -9010,10 +9186,10 @@
         <v>-4247.291631430095</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>1170.747459307867</v>
+        <v>1177.726820531765</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>1997.519223331204</v>
+        <v>1944.112617987525</v>
       </c>
     </row>
     <row r="23">
@@ -9080,10 +9256,10 @@
         <v>-2197.047861439517</v>
       </c>
       <c r="U23" s="2" t="n">
-        <v>404.7137215801117</v>
+        <v>402.6132148135748</v>
       </c>
       <c r="V23" s="2" t="n">
-        <v>451.1378619539349</v>
+        <v>447.4519670628269</v>
       </c>
     </row>
     <row r="24">
@@ -9150,10 +9326,10 @@
         <v>-3960.099070098704</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>867.5878838378176</v>
+        <v>880.9991435769896</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>1123.229104986674</v>
+        <v>1074.896674441316</v>
       </c>
     </row>
     <row r="25">
@@ -9220,10 +9396,10 @@
         <v>-183.1175254871977</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>62.21132896172385</v>
+        <v>61.21484805658388</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>91.05762296847006</v>
+        <v>89.98594557901284</v>
       </c>
     </row>
     <row r="26">
@@ -9290,10 +9466,10 @@
         <v>-3723.200094274174</v>
       </c>
       <c r="U26" s="2" t="n">
-        <v>784.46593252424</v>
+        <v>792.8138985938697</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>1060.066638366531</v>
+        <v>1031.42509065577</v>
       </c>
     </row>
     <row r="27">
@@ -9360,10 +9536,10 @@
         <v>-515875.0824275783</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>1396.110481412234</v>
+        <v>1387.5830409054</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>1791.970648794605</v>
+        <v>1742.087801781186</v>
       </c>
     </row>
     <row r="28">
@@ -9430,10 +9606,10 @@
         <v>-776330.1662227859</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>4272.356769265682</v>
+        <v>4226.450941576512</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>6183.814465841818</v>
+        <v>5978.972399413969</v>
       </c>
     </row>
     <row r="29">
@@ -9500,10 +9676,10 @@
         <v>-469150.6563444739</v>
       </c>
       <c r="U29" s="2" t="n">
-        <v>7111.481387480448</v>
+        <v>6996.07311669923</v>
       </c>
       <c r="V29" s="2" t="n">
-        <v>22221.23780552813</v>
+        <v>20789.96132187671</v>
       </c>
     </row>
     <row r="30">
@@ -9570,10 +9746,10 @@
         <v>-1276833.767350986</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>3625.117860258839</v>
+        <v>3567.667946771464</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>4929.191671337281</v>
+        <v>4954.168964716645</v>
       </c>
     </row>
     <row r="31">
@@ -9640,10 +9816,10 @@
         <v>-129126.8427564082</v>
       </c>
       <c r="U31" s="2" t="n">
-        <v>1957.995773255892</v>
+        <v>1958.674130821249</v>
       </c>
       <c r="V31" s="2" t="n">
-        <v>3172.82826556263</v>
+        <v>3084.901189558607</v>
       </c>
     </row>
     <row r="32">
@@ -9710,10 +9886,10 @@
         <v>-281.1464644136773</v>
       </c>
       <c r="U32" s="2" t="n">
-        <v>120.0279866406557</v>
+        <v>116.0665012966474</v>
       </c>
       <c r="V32" s="2" t="n">
-        <v>336.9494925688513</v>
+        <v>339.6228389540004</v>
       </c>
     </row>
     <row r="33">
@@ -9780,10 +9956,10 @@
         <v>-142542.658222201</v>
       </c>
       <c r="U33" s="2" t="n">
-        <v>3147.130469643701</v>
+        <v>3155.540169613117</v>
       </c>
       <c r="V33" s="2" t="n">
-        <v>6101.175243213745</v>
+        <v>6096.553542412496</v>
       </c>
     </row>
     <row r="34">
@@ -9850,10 +10026,10 @@
         <v>-338.7052817524378</v>
       </c>
       <c r="U34" s="2" t="n">
-        <v>79.17110198357663</v>
+        <v>77.44595069676913</v>
       </c>
       <c r="V34" s="2" t="n">
-        <v>95.6891317693579</v>
+        <v>95.67255553115217</v>
       </c>
     </row>
     <row r="35">
@@ -9920,10 +10096,10 @@
         <v>-489.0773369178513</v>
       </c>
       <c r="U35" s="2" t="n">
-        <v>130.4030899866756</v>
+        <v>128.8476464468499</v>
       </c>
       <c r="V35" s="2" t="n">
-        <v>197.1133272124989</v>
+        <v>189.6907153599787</v>
       </c>
     </row>
     <row r="36">
@@ -9990,10 +10166,10 @@
         <v>-289768.0638616111</v>
       </c>
       <c r="U36" s="2" t="n">
-        <v>6842.579789311775</v>
+        <v>6783.082741168938</v>
       </c>
       <c r="V36" s="2" t="n">
-        <v>16102.17860467124</v>
+        <v>15274.19021141982</v>
       </c>
     </row>
     <row r="37">
@@ -10060,10 +10236,10 @@
         <v>-5160.738295185893</v>
       </c>
       <c r="U37" s="2" t="n">
-        <v>1565.407333498962</v>
+        <v>1554.137513204355</v>
       </c>
       <c r="V37" s="2" t="n">
-        <v>4792.492519227893</v>
+        <v>4550.070821322682</v>
       </c>
     </row>
     <row r="38">
@@ -10130,10 +10306,10 @@
         <v>-69430.65177444747</v>
       </c>
       <c r="U38" s="2" t="n">
-        <v>4080.647402731488</v>
+        <v>4014.185728658158</v>
       </c>
       <c r="V38" s="2" t="n">
-        <v>14818.48555181959</v>
+        <v>14860.28288827575</v>
       </c>
     </row>
     <row r="39">
@@ -10200,10 +10376,10 @@
         <v>-248180.079411032</v>
       </c>
       <c r="U39" s="2" t="n">
-        <v>8314.74303428719</v>
+        <v>8174.14203819047</v>
       </c>
       <c r="V39" s="2" t="n">
-        <v>30505.99869998294</v>
+        <v>30078.7151971144</v>
       </c>
     </row>
     <row r="40">
@@ -10270,10 +10446,10 @@
         <v>-41506.56000784492</v>
       </c>
       <c r="U40" s="2" t="n">
-        <v>12954.50140844745</v>
+        <v>13278.63576068403</v>
       </c>
       <c r="V40" s="2" t="n">
-        <v>47478.89492498648</v>
+        <v>47003.1815902428</v>
       </c>
     </row>
     <row r="41">
@@ -10340,10 +10516,10 @@
         <v>-736674.0387455032</v>
       </c>
       <c r="U41" s="2" t="n">
-        <v>30909.15921150354</v>
+        <v>30898.38479854625</v>
       </c>
       <c r="V41" s="2" t="n">
-        <v>171852.9900596889</v>
+        <v>163593.2508741701</v>
       </c>
     </row>
     <row r="42">
@@ -10410,10 +10586,10 @@
         <v>-997488.464398687</v>
       </c>
       <c r="U42" s="2" t="n">
-        <v>57908.33813053989</v>
+        <v>58369.57862654355</v>
       </c>
       <c r="V42" s="2" t="n">
-        <v>825323.5132043958</v>
+        <v>764649.1711995355</v>
       </c>
     </row>
     <row r="43">
@@ -10480,10 +10656,10 @@
         <v>-1176981.003390645</v>
       </c>
       <c r="U43" s="2" t="n">
-        <v>73636.11935477474</v>
+        <v>72972.11432948947</v>
       </c>
       <c r="V43" s="2" t="n">
-        <v>387883.9952821227</v>
+        <v>370142.7189656865</v>
       </c>
     </row>
     <row r="44">
@@ -10550,10 +10726,10 @@
         <v>-52.36494957223326</v>
       </c>
       <c r="U44" s="2" t="n">
-        <v>83.16343564623789</v>
+        <v>82.8832399349007</v>
       </c>
       <c r="V44" s="2" t="n">
-        <v>256.5575742259127</v>
+        <v>254.0608779579962</v>
       </c>
     </row>
     <row r="45">
@@ -10620,10 +10796,10 @@
         <v>-1521263.570691504</v>
       </c>
       <c r="U45" s="2" t="n">
-        <v>115740.8069178312</v>
+        <v>113956.1273752487</v>
       </c>
       <c r="V45" s="2" t="n">
-        <v>579004.4859692617</v>
+        <v>559821.9794233225</v>
       </c>
     </row>
     <row r="46">
@@ -10690,10 +10866,10 @@
         <v>-1839156.242741637</v>
       </c>
       <c r="U46" s="2" t="n">
-        <v>75602.39173724233</v>
+        <v>74741.15397557055</v>
       </c>
       <c r="V46" s="2" t="n">
-        <v>303137.1428912739</v>
+        <v>295987.2470950339</v>
       </c>
     </row>
   </sheetData>
@@ -10974,7 +11150,7 @@
         <v>-32.12008939505308</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>1.885526763619611</v>
+        <v>1.878087883662399</v>
       </c>
       <c r="V3" s="2" t="n">
         <v>0.4259477184223214</v>
@@ -11114,10 +11290,10 @@
         <v>-6.936026818515923</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>5.573258916817597</v>
+        <v>5.564543770877899</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>7.912069298334329</v>
+        <v>7.860853305148327</v>
       </c>
     </row>
     <row r="6">
@@ -11184,10 +11360,10 @@
         <v>-37.05265155629453</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>26.00759147380568</v>
+        <v>25.85536647293242</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>46.08849811427029</v>
+        <v>45.1319016450555</v>
       </c>
     </row>
     <row r="7">
@@ -11254,10 +11430,10 @@
         <v>-381.5210791259988</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>46.78419474590279</v>
+        <v>46.81788282657553</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>49.9240741166841</v>
+        <v>48.19726778794774</v>
       </c>
     </row>
     <row r="8">
@@ -11324,10 +11500,10 @@
         <v>-691.7086970186991</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>122.2161732212628</v>
+        <v>122.9263253691878</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>142.875060451637</v>
+        <v>140.8975049144198</v>
       </c>
     </row>
     <row r="9">
@@ -11394,10 +11570,10 @@
         <v>-2693.977387312212</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>704.2167047695989</v>
+        <v>696.0748825189173</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>1292.346285248439</v>
+        <v>1245.601022174115</v>
       </c>
     </row>
     <row r="10">
@@ -11464,10 +11640,10 @@
         <v>-294.0670879706451</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>81.56068422723456</v>
+        <v>78.98789308582147</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>381.6550301355535</v>
+        <v>372.1770603168501</v>
       </c>
     </row>
     <row r="11">
@@ -11534,10 +11710,10 @@
         <v>-2740.128088028211</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>635.4477202265841</v>
+        <v>625.1285737256148</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>1200.925063995364</v>
+        <v>1187.940441684514</v>
       </c>
     </row>
     <row r="12">
@@ -11604,10 +11780,10 @@
         <v>-1962.486373887568</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>544.535234028796</v>
+        <v>538.0635050414182</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>1516.750908149784</v>
+        <v>1480.145124117653</v>
       </c>
     </row>
     <row r="13">
@@ -11674,10 +11850,10 @@
         <v>-8012.255817084662</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>2682.653877785121</v>
+        <v>2656.820722305619</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>5517.186157857227</v>
+        <v>5385.081532208244</v>
       </c>
     </row>
     <row r="14">
@@ -11744,10 +11920,10 @@
         <v>-2677.846064808891</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>416.4953224849871</v>
+        <v>415.453035315079</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>466.6458401192457</v>
+        <v>450.3766805784952</v>
       </c>
     </row>
     <row r="15">
@@ -11814,10 +11990,10 @@
         <v>-6300.958291831585</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>1578.476502816931</v>
+        <v>1546.315964048102</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>2565.706682080251</v>
+        <v>2470.640553309572</v>
       </c>
     </row>
     <row r="16">
@@ -11884,10 +12060,10 @@
         <v>-4414.739473613688</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>804.3061887645554</v>
+        <v>805.7689636070436</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>967.6178850340229</v>
+        <v>945.5745855891123</v>
       </c>
     </row>
     <row r="17">
@@ -11954,10 +12130,10 @@
         <v>-10416.99276788139</v>
       </c>
       <c r="U17" s="2" t="n">
-        <v>2610.242807601143</v>
+        <v>2575.217274091175</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>3926.182263050561</v>
+        <v>3752.059359788516</v>
       </c>
     </row>
     <row r="18">
@@ -12024,10 +12200,10 @@
         <v>-2227.375206310696</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>427.8088859179441</v>
+        <v>437.215420181951</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>516.4626068550535</v>
+        <v>511.2901281751808</v>
       </c>
     </row>
     <row r="19">
@@ -12094,10 +12270,10 @@
         <v>-21771.78477101872</v>
       </c>
       <c r="U19" s="2" t="n">
-        <v>6531.410212089685</v>
+        <v>6494.006213848326</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>12271.79095245749</v>
+        <v>12063.0585809616</v>
       </c>
     </row>
     <row r="20">
@@ -12164,10 +12340,10 @@
         <v>-1352.06415948961</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>266.4016559510214</v>
+        <v>266.0138208353769</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>326.8931365174002</v>
+        <v>316.4796075179043</v>
       </c>
     </row>
     <row r="21">
@@ -12234,10 +12410,10 @@
         <v>-1079545.542005932</v>
       </c>
       <c r="U21" s="2" t="n">
-        <v>1188.169272993436</v>
+        <v>1199.786342243728</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>1564.336459080952</v>
+        <v>1524.681824908291</v>
       </c>
     </row>
     <row r="22">
@@ -12304,10 +12480,10 @@
         <v>-4249.608379308297</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>1170.763514634156</v>
+        <v>1177.743138429179</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>1997.53797122351</v>
+        <v>1944.131304242527</v>
       </c>
     </row>
     <row r="23">
@@ -12374,10 +12550,10 @@
         <v>-2197.047861439517</v>
       </c>
       <c r="U23" s="2" t="n">
-        <v>404.7137215801117</v>
+        <v>402.6132148135748</v>
       </c>
       <c r="V23" s="2" t="n">
-        <v>451.1378619539349</v>
+        <v>447.4519670628269</v>
       </c>
     </row>
     <row r="24">
@@ -12444,10 +12620,10 @@
         <v>-3960.824758142686</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>867.5928026695827</v>
+        <v>881.0041588872872</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>1123.234724787333</v>
+        <v>1074.902147437991</v>
       </c>
     </row>
     <row r="25">
@@ -12514,10 +12690,10 @@
         <v>-183.1175254871977</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>62.21132896172385</v>
+        <v>61.21484805658388</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>91.05762296847006</v>
+        <v>89.98594557901284</v>
       </c>
     </row>
     <row r="26">
@@ -12584,10 +12760,10 @@
         <v>-3723.200094274174</v>
       </c>
       <c r="U26" s="2" t="n">
-        <v>784.46593252424</v>
+        <v>792.8138985938697</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>1060.066638366531</v>
+        <v>1031.42509065577</v>
       </c>
     </row>
     <row r="27">
@@ -12654,10 +12830,10 @@
         <v>-515946.3680728071</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>1396.127269689836</v>
+        <v>1387.599918116585</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>1791.98932777158</v>
+        <v>1742.10620191493</v>
       </c>
     </row>
     <row r="28">
@@ -12724,10 +12900,10 @@
         <v>-776414.3528684906</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>4272.437593817341</v>
+        <v>4226.531839368787</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>6183.905376245774</v>
+        <v>5979.06236232317</v>
       </c>
     </row>
     <row r="29">
@@ -12794,10 +12970,10 @@
         <v>-469234.8648726935</v>
       </c>
       <c r="U29" s="2" t="n">
-        <v>7111.563027966773</v>
+        <v>6996.154042781822</v>
       </c>
       <c r="V29" s="2" t="n">
-        <v>22221.399074659</v>
+        <v>20790.11571925702</v>
       </c>
     </row>
     <row r="30">
@@ -12864,10 +13040,10 @@
         <v>-1276978.283422939</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>3625.175155606765</v>
+        <v>3567.724626425783</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>4929.254975867771</v>
+        <v>4954.233598999737</v>
       </c>
     </row>
     <row r="31">
@@ -12934,10 +13110,10 @@
         <v>-129143.7249648278</v>
       </c>
       <c r="U31" s="2" t="n">
-        <v>1958.007267251339</v>
+        <v>1958.685750953317</v>
       </c>
       <c r="V31" s="2" t="n">
-        <v>3172.84440321039</v>
+        <v>3084.917054187977</v>
       </c>
     </row>
     <row r="32">
@@ -13004,10 +13180,10 @@
         <v>-281.1472957359411</v>
       </c>
       <c r="U32" s="2" t="n">
-        <v>120.0279971750162</v>
+        <v>116.0665113958183</v>
       </c>
       <c r="V32" s="2" t="n">
-        <v>336.9495352068186</v>
+        <v>339.6228820649721</v>
       </c>
     </row>
     <row r="33">
@@ -13074,10 +13250,10 @@
         <v>-142557.8515240963</v>
       </c>
       <c r="U33" s="2" t="n">
-        <v>3147.138752122165</v>
+        <v>3155.548467823493</v>
       </c>
       <c r="V33" s="2" t="n">
-        <v>6101.185372512154</v>
+        <v>6096.563991926266</v>
       </c>
     </row>
     <row r="34">
@@ -13144,10 +13320,10 @@
         <v>-338.7052817524378</v>
       </c>
       <c r="U34" s="2" t="n">
-        <v>79.17110198357663</v>
+        <v>77.44595069676913</v>
       </c>
       <c r="V34" s="2" t="n">
-        <v>95.6891317693579</v>
+        <v>95.67255553115217</v>
       </c>
     </row>
     <row r="35">
@@ -13214,10 +13390,10 @@
         <v>-489.07736109112</v>
       </c>
       <c r="U35" s="2" t="n">
-        <v>130.4030903106927</v>
+        <v>128.8476467581015</v>
       </c>
       <c r="V35" s="2" t="n">
-        <v>197.1133286981821</v>
+        <v>189.6907167790037</v>
       </c>
     </row>
     <row r="36">
@@ -13284,10 +13460,10 @@
         <v>-289813.5861201417</v>
       </c>
       <c r="U36" s="2" t="n">
-        <v>6842.656220261715</v>
+        <v>6783.158943214275</v>
       </c>
       <c r="V36" s="2" t="n">
-        <v>16102.29805462842</v>
+        <v>15274.30670656247</v>
       </c>
     </row>
     <row r="37">
@@ -13354,10 +13530,10 @@
         <v>-5162.630056114262</v>
       </c>
       <c r="U37" s="2" t="n">
-        <v>1565.421137446049</v>
+        <v>1554.151412555387</v>
       </c>
       <c r="V37" s="2" t="n">
-        <v>4792.518686655595</v>
+        <v>4550.096146409545</v>
       </c>
     </row>
     <row r="38">
@@ -13424,10 +13600,10 @@
         <v>-69439.82694097792</v>
       </c>
       <c r="U38" s="2" t="n">
-        <v>4080.669074926836</v>
+        <v>4014.207129286133</v>
       </c>
       <c r="V38" s="2" t="n">
-        <v>14818.53865673045</v>
+        <v>14860.33632780813</v>
       </c>
     </row>
     <row r="39">
@@ -13494,10 +13670,10 @@
         <v>-248214.509275</v>
       </c>
       <c r="U39" s="2" t="n">
-        <v>8314.811519317826</v>
+        <v>8174.210057567542</v>
       </c>
       <c r="V39" s="2" t="n">
-        <v>30506.17458210583</v>
+        <v>30078.89094918133</v>
       </c>
     </row>
     <row r="40">
@@ -13564,10 +13740,10 @@
         <v>-41513.75162142119</v>
       </c>
       <c r="U40" s="2" t="n">
-        <v>12954.56807151486</v>
+        <v>13278.70463473468</v>
       </c>
       <c r="V40" s="2" t="n">
-        <v>47479.0548979713</v>
+        <v>47003.34151131392</v>
       </c>
     </row>
     <row r="41">
@@ -13634,10 +13810,10 @@
         <v>-737148.9306342942</v>
       </c>
       <c r="U41" s="2" t="n">
-        <v>30909.46960630374</v>
+        <v>30898.69653806371</v>
       </c>
       <c r="V41" s="2" t="n">
-        <v>171854.0414219709</v>
+        <v>163594.2759401503</v>
       </c>
     </row>
     <row r="42">
@@ -13704,10 +13880,10 @@
         <v>-997628.8321798523</v>
       </c>
       <c r="U42" s="2" t="n">
-        <v>57908.71410554681</v>
+        <v>58369.96191435331</v>
       </c>
       <c r="V42" s="2" t="n">
-        <v>825326.935578486</v>
+        <v>764652.412024294</v>
       </c>
     </row>
     <row r="43">
@@ -13774,10 +13950,10 @@
         <v>-1350008.074881661</v>
       </c>
       <c r="U43" s="2" t="n">
-        <v>73673.54983970542</v>
+        <v>73009.30267190243</v>
       </c>
       <c r="V43" s="2" t="n">
-        <v>387990.1671907493</v>
+        <v>370247.5739143033</v>
       </c>
     </row>
     <row r="44">
@@ -13844,10 +14020,10 @@
         <v>-52.36494957223341</v>
       </c>
       <c r="U44" s="2" t="n">
-        <v>83.16343564623789</v>
+        <v>82.8832399349007</v>
       </c>
       <c r="V44" s="2" t="n">
-        <v>256.5575742259127</v>
+        <v>254.0608779579962</v>
       </c>
     </row>
     <row r="45">
@@ -13914,10 +14090,10 @@
         <v>-1521455.619227816</v>
       </c>
       <c r="U45" s="2" t="n">
-        <v>115741.3004196454</v>
+        <v>113956.617173022</v>
       </c>
       <c r="V45" s="2" t="n">
-        <v>579006.1777987792</v>
+        <v>559823.6405459424</v>
       </c>
     </row>
     <row r="46">
@@ -13984,10 +14160,10 @@
         <v>-1839436.878999577</v>
       </c>
       <c r="U46" s="2" t="n">
-        <v>75603.00312440246</v>
+        <v>74741.7620801836</v>
       </c>
       <c r="V46" s="2" t="n">
-        <v>303138.8392245189</v>
+        <v>295988.9330012708</v>
       </c>
     </row>
   </sheetData>
@@ -15439,22 +15615,22 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>1277.339696689196</v>
+        <v>1271.23152900969</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>1277.328774419787</v>
+        <v>1271.220590789812</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>492.2469939583181</v>
+        <v>490.4187121959304</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>4116</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.3103325496646714</v>
+        <v>0.3088485400363974</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.1195935359471132</v>
+        <v>0.1191493469863776</v>
       </c>
     </row>
     <row r="21">
@@ -15464,22 +15640,22 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>3887.672043339526</v>
+        <v>3734.376511853387</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>3887.648813915192</v>
+        <v>3734.35379319916</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>3146.390831562344</v>
+        <v>3024.331675928972</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>4116</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.9445210918161303</v>
+        <v>0.90727740359552</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.7644292593688882</v>
+        <v>0.7347744596523256</v>
       </c>
     </row>
   </sheetData>
@@ -15555,10 +15731,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -15583,10 +15759,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -15782,7 +15958,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Christensen &amp; Pauly (1995): per-group TE^(1-TL) with global_TE=0.1.</t>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE=0.1.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -15799,7 +15975,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Christensen &amp; Pauly (1995): per-group TE^(1-TL) with global_TE='mean'.</t>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">

--- a/PPREstimation/output/top10/28_646_Guinea_(1998).xlsx
+++ b/PPREstimation/output/top10/28_646_Guinea_(1998).xlsx
@@ -617,7 +617,6 @@
           <t>Import</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="2" t="n">
         <v>1</v>
       </c>
@@ -4565,7 +4564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V46"/>
+  <dimension ref="A1:X46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4703,6 +4702,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -4713,9 +4722,6 @@
           <t>diet_import</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
@@ -4746,19 +4752,19 @@
       <c r="O2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4771,9 +4777,6 @@
           <t>Detritus</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
@@ -4823,6 +4826,9 @@
         <v>0</v>
       </c>
       <c r="V3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4835,9 +4841,6 @@
           <t>Producteurs primaires</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" s="2" t="n">
         <v>1</v>
       </c>
@@ -4887,6 +4890,9 @@
         <v>1</v>
       </c>
       <c r="V4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4899,11 +4905,8 @@
           <t>Zool S</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" s="2" t="n">
-        <v>7.388359670874971</v>
+        <v>8.845979986780915</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>7.500000000000001</v>
@@ -4952,6 +4955,9 @@
       </c>
       <c r="V5" s="2" t="n">
         <v>7.505630400226367</v>
+      </c>
+      <c r="X5" t="n">
+        <v>7.388359670874971</v>
       </c>
     </row>
     <row r="6">
@@ -4963,11 +4969,8 @@
           <t>Zool L</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" s="2" t="n">
-        <v>48.13040632836959</v>
+        <v>68.80073366818922</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>37.1875</v>
@@ -5016,6 +5019,9 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>42.83231604378508</v>
+      </c>
+      <c r="X6" t="n">
+        <v>48.13040632836959</v>
       </c>
     </row>
     <row r="7">
@@ -5027,11 +5033,8 @@
           <t>Benthos</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" s="2" t="n">
-        <v>9.344255093397782</v>
+        <v>13.33675965398077</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>21.68600282830268</v>
@@ -5080,6 +5083,9 @@
       </c>
       <c r="V7" s="2" t="n">
         <v>35.95337081765199</v>
+      </c>
+      <c r="X7" t="n">
+        <v>9.344255093397782</v>
       </c>
     </row>
     <row r="8">
@@ -5091,11 +5097,8 @@
           <t>Crustacés</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" s="2" t="n">
-        <v>83.93179990196712</v>
+        <v>141.8605355521422</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>58.60957479100993</v>
@@ -5144,6 +5147,9 @@
       </c>
       <c r="V8" s="2" t="n">
         <v>109.873168166362</v>
+      </c>
+      <c r="X8" t="n">
+        <v>83.93179990196712</v>
       </c>
     </row>
     <row r="9">
@@ -5155,11 +5161,8 @@
           <t>Céphalopodes</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" s="2" t="n">
-        <v>1022.837476894869</v>
+        <v>2209.641323217027</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>533.9372432131269</v>
@@ -5208,6 +5211,9 @@
       </c>
       <c r="V9" s="2" t="n">
         <v>1017.651066096116</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1022.837476894869</v>
       </c>
     </row>
     <row r="10">
@@ -5219,11 +5225,8 @@
           <t>Mésopélagiques</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" s="2" t="n">
-        <v>145.0666697547654</v>
+        <v>243.2317226965979</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>199.5213778081198</v>
@@ -5272,6 +5275,9 @@
       </c>
       <c r="V10" s="2" t="n">
         <v>318.2118543021983</v>
+      </c>
+      <c r="X10" t="n">
+        <v>145.0666697547654</v>
       </c>
     </row>
     <row r="11">
@@ -5283,11 +5289,8 @@
           <t>Bathy SM inv</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" s="2" t="n">
-        <v>353.2383408704655</v>
+        <v>661.2789662055947</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>629.2711980675266</v>
@@ -5336,6 +5339,9 @@
       </c>
       <c r="V11" s="2" t="n">
         <v>990.3410206887481</v>
+      </c>
+      <c r="X11" t="n">
+        <v>353.2383408704655</v>
       </c>
     </row>
     <row r="12">
@@ -5347,11 +5353,8 @@
           <t>Bathy S pred</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" s="2" t="n">
-        <v>660.5377108878633</v>
+        <v>1316.465337045587</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>767.8792396070533</v>
@@ -5400,6 +5403,9 @@
       </c>
       <c r="V12" s="2" t="n">
         <v>1250.020162688867</v>
+      </c>
+      <c r="X12" t="n">
+        <v>660.5377108878633</v>
       </c>
     </row>
     <row r="13">
@@ -5411,11 +5417,8 @@
           <t>Bathy L pred</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" s="2" t="n">
-        <v>2201.333705289991</v>
+        <v>5440.782564284679</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>2144.122371059091</v>
@@ -5464,6 +5467,9 @@
       </c>
       <c r="V13" s="2" t="n">
         <v>4425.550085170168</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2201.333705289991</v>
       </c>
     </row>
     <row r="14">
@@ -5475,11 +5481,8 @@
           <t>Dem S inv</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" s="2" t="n">
-        <v>76.70968609603133</v>
+        <v>131.0852322084679</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>200.277881135268</v>
@@ -5528,6 +5531,9 @@
       </c>
       <c r="V14" s="2" t="n">
         <v>336.0173740224187</v>
+      </c>
+      <c r="X14" t="n">
+        <v>76.70968609603133</v>
       </c>
     </row>
     <row r="15">
@@ -5539,11 +5545,8 @@
           <t>Dem S pred</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" s="2" t="n">
-        <v>927.7647380155879</v>
+        <v>2046.175316920372</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>964.5167956618869</v>
@@ -5592,6 +5595,9 @@
       </c>
       <c r="V15" s="2" t="n">
         <v>1986.22292772838</v>
+      </c>
+      <c r="X15" t="n">
+        <v>927.7647380155879</v>
       </c>
     </row>
     <row r="16">
@@ -5603,11 +5609,8 @@
           <t>Dem M inv</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" s="2" t="n">
-        <v>189.5328086581246</v>
+        <v>356.6104776328821</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>425.6407433503436</v>
@@ -5656,6 +5659,9 @@
       </c>
       <c r="V16" s="2" t="n">
         <v>730.0932695810826</v>
+      </c>
+      <c r="X16" t="n">
+        <v>189.5328086581246</v>
       </c>
     </row>
     <row r="17">
@@ -5667,11 +5673,8 @@
           <t>Dem M pred</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" s="2" t="n">
-        <v>1719.62241153043</v>
+        <v>4156.7157124966</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>1627.447793929556</v>
@@ -5720,6 +5723,9 @@
       </c>
       <c r="V17" s="2" t="n">
         <v>2978.125002299211</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1719.62241153043</v>
       </c>
     </row>
     <row r="18">
@@ -5731,11 +5737,8 @@
           <t>Dem L inv</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" s="2" t="n">
-        <v>213.1518579528482</v>
+        <v>415.1282253974796</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>220.3439969180131</v>
@@ -5784,6 +5787,9 @@
       </c>
       <c r="V18" s="2" t="n">
         <v>395.1192515551665</v>
+      </c>
+      <c r="X18" t="n">
+        <v>213.1518579528482</v>
       </c>
     </row>
     <row r="19">
@@ -5795,11 +5801,8 @@
           <t>Dem L pred</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" s="2" t="n">
-        <v>2496.813504239259</v>
+        <v>6647.368801517983</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>4415.463104531551</v>
@@ -5848,6 +5851,9 @@
       </c>
       <c r="V19" s="2" t="n">
         <v>9644.194140463422</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2496.813504239259</v>
       </c>
     </row>
     <row r="20">
@@ -5859,11 +5865,8 @@
           <t>Côtier S inv</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" s="2" t="n">
-        <v>141.3259885532719</v>
+        <v>269.0229133412283</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>143.357992975312</v>
@@ -5912,6 +5915,9 @@
       </c>
       <c r="V20" s="2" t="n">
         <v>248.3211962608204</v>
+      </c>
+      <c r="X20" t="n">
+        <v>141.3259885532719</v>
       </c>
     </row>
     <row r="21">
@@ -5923,11 +5929,8 @@
           <t>Capitaine royal</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" s="2" t="n">
-        <v>745.7132034114375</v>
+        <v>1549.34916140667</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>688.3080887895044</v>
@@ -5976,6 +5979,9 @@
       </c>
       <c r="V21" s="2" t="n">
         <v>1212.163930138708</v>
+      </c>
+      <c r="X21" t="n">
+        <v>745.7132034114375</v>
       </c>
     </row>
     <row r="22">
@@ -5987,11 +5993,8 @@
           <t>Côtier S pred</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" s="2" t="n">
-        <v>1523.664607001135</v>
+        <v>3699.936690977708</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>857.0177019772957</v>
@@ -6040,6 +6043,9 @@
       </c>
       <c r="V22" s="2" t="n">
         <v>1572.808567304289</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1523.664607001135</v>
       </c>
     </row>
     <row r="23">
@@ -6051,11 +6057,8 @@
           <t>Côtier M inv</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" s="2" t="n">
-        <v>208.5097401148763</v>
+        <v>398.1683639745834</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>199.1916445665024</v>
@@ -6104,6 +6107,9 @@
       </c>
       <c r="V23" s="2" t="n">
         <v>344.6650991948791</v>
+      </c>
+      <c r="X23" t="n">
+        <v>208.5097401148763</v>
       </c>
     </row>
     <row r="24">
@@ -6115,11 +6121,8 @@
           <t>Petit capitaine</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" s="2" t="n">
-        <v>601.9521504197585</v>
+        <v>1224.050099244793</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>463.1775764434879</v>
@@ -6168,6 +6171,9 @@
       </c>
       <c r="V24" s="2" t="n">
         <v>840.2198830872899</v>
+      </c>
+      <c r="X24" t="n">
+        <v>601.9521504197585</v>
       </c>
     </row>
     <row r="25">
@@ -6179,11 +6185,8 @@
           <t>Mulets</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" s="2" t="n">
-        <v>54.45821226675307</v>
+        <v>89.51813904323544</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>70.58587414581179</v>
@@ -6232,6 +6235,9 @@
       </c>
       <c r="V25" s="2" t="n">
         <v>82.33755050988032</v>
+      </c>
+      <c r="X25" t="n">
+        <v>54.45821226675307</v>
       </c>
     </row>
     <row r="26">
@@ -6243,11 +6249,8 @@
           <t>Disques</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" s="2" t="n">
-        <v>307.7831604612996</v>
+        <v>591.7698295695509</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>490.2532816831419</v>
@@ -6296,6 +6299,9 @@
       </c>
       <c r="V26" s="2" t="n">
         <v>817.7492438310887</v>
+      </c>
+      <c r="X26" t="n">
+        <v>307.7831604612996</v>
       </c>
     </row>
     <row r="27">
@@ -6307,11 +6313,8 @@
           <t>Mâchoiron</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" s="2" t="n">
-        <v>729.6577258012351</v>
+        <v>1654.813793510237</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>773.8790652912654</v>
@@ -6360,6 +6363,9 @@
       </c>
       <c r="V27" s="2" t="n">
         <v>1370.742426914867</v>
+      </c>
+      <c r="X27" t="n">
+        <v>729.6577258012351</v>
       </c>
     </row>
     <row r="28">
@@ -6371,11 +6377,8 @@
           <t>Côtier M pred</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" s="2" t="n">
-        <v>1625.586348117391</v>
+        <v>4166.421230034628</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>2699.893953178272</v>
@@ -6424,6 +6427,9 @@
       </c>
       <c r="V28" s="2" t="n">
         <v>4781.767213139441</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1625.586348117391</v>
       </c>
     </row>
     <row r="29">
@@ -6435,11 +6441,8 @@
           <t>Côtier L pred</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" s="2" t="n">
-        <v>2083.221444075729</v>
+        <v>5244.468733123034</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>3323.212634459693</v>
@@ -6488,6 +6491,9 @@
       </c>
       <c r="V29" s="2" t="n">
         <v>16812.29830107797</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2083.221444075729</v>
       </c>
     </row>
     <row r="30">
@@ -6499,11 +6505,8 @@
           <t>Gros capitaine</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" s="2" t="n">
-        <v>2479.254500604849</v>
+        <v>6576.017498875481</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>2190.960534220797</v>
@@ -6552,6 +6555,9 @@
       </c>
       <c r="V30" s="2" t="n">
         <v>3943.075354225288</v>
+      </c>
+      <c r="X30" t="n">
+        <v>2479.254500604849</v>
       </c>
     </row>
     <row r="31">
@@ -6563,11 +6569,8 @@
           <t>Bars</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" s="2" t="n">
-        <v>1058.131618941768</v>
+        <v>2420.685090093484</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>897.7118168365503</v>
@@ -6616,6 +6619,9 @@
       </c>
       <c r="V31" s="2" t="n">
         <v>2463.064614465615</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1058.131618941768</v>
       </c>
     </row>
     <row r="32">
@@ -6627,11 +6633,8 @@
           <t>Pel S inv</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" s="2" t="n">
-        <v>263.2939568891615</v>
+        <v>486.9739453814768</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>190.9337229061146</v>
@@ -6680,6 +6683,9 @@
       </c>
       <c r="V32" s="2" t="n">
         <v>297.1981429492287</v>
+      </c>
+      <c r="X32" t="n">
+        <v>263.2939568891615</v>
       </c>
     </row>
     <row r="33">
@@ -6691,11 +6697,8 @@
           <t>Pel L pred</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" s="2" t="n">
-        <v>1691.840322827748</v>
+        <v>3931.194333518501</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>2174.355127156889</v>
@@ -6744,6 +6747,9 @@
       </c>
       <c r="V33" s="2" t="n">
         <v>5057.925718751013</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1691.840322827748</v>
       </c>
     </row>
     <row r="34">
@@ -6755,11 +6761,8 @@
           <t>Ethmalose</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" s="2" t="n">
-        <v>36.03688337173888</v>
+        <v>52.80133962529329</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>62.49105656551363</v>
@@ -6808,6 +6811,9 @@
       </c>
       <c r="V34" s="2" t="n">
         <v>80.23133492244214</v>
+      </c>
+      <c r="X34" t="n">
+        <v>36.03688337173888</v>
       </c>
     </row>
     <row r="35">
@@ -6819,11 +6825,8 @@
           <t>Côtier pel S inv</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" s="2" t="n">
-        <v>140.1396279107831</v>
+        <v>251.2253997466582</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>86.15874253148233</v>
@@ -6872,6 +6875,9 @@
       </c>
       <c r="V35" s="2" t="n">
         <v>159.5096477892282</v>
+      </c>
+      <c r="X35" t="n">
+        <v>140.1396279107831</v>
       </c>
     </row>
     <row r="36">
@@ -6883,11 +6889,8 @@
           <t>Côtier pel L pred</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" s="2" t="n">
-        <v>3330.282942456625</v>
+        <v>8886.57437490064</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>4351.939948763842</v>
@@ -6936,6 +6939,9 @@
       </c>
       <c r="V36" s="2" t="n">
         <v>12354.97382371667</v>
+      </c>
+      <c r="X36" t="n">
+        <v>3330.282942456625</v>
       </c>
     </row>
     <row r="37">
@@ -6947,11 +6953,8 @@
           <t>Thons mineurs</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" s="2" t="n">
-        <v>2895.40308940724</v>
+        <v>7097.856680652434</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>2048.262998787421</v>
@@ -7000,6 +7003,9 @@
       </c>
       <c r="V37" s="2" t="n">
         <v>3726.667281850449</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2895.40308940724</v>
       </c>
     </row>
     <row r="38">
@@ -7011,11 +7017,8 @@
           <t>Thons majeurs</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" s="2" t="n">
-        <v>5199.941546665721</v>
+        <v>13661.71045170092</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>5828.690681648573</v>
@@ -7064,6 +7067,9 @@
       </c>
       <c r="V38" s="2" t="n">
         <v>12125.41410542123</v>
+      </c>
+      <c r="X38" t="n">
+        <v>5199.941546665721</v>
       </c>
     </row>
     <row r="39">
@@ -7075,11 +7081,8 @@
           <t>Sélaciens M côtiers</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" s="2" t="n">
-        <v>3255.127341270281</v>
+        <v>8688.631575014309</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>10752.12099995471</v>
@@ -7128,6 +7131,9 @@
       </c>
       <c r="V39" s="2" t="n">
         <v>24373.86353893469</v>
+      </c>
+      <c r="X39" t="n">
+        <v>3255.127341270281</v>
       </c>
     </row>
     <row r="40">
@@ -7139,11 +7145,8 @@
           <t>Sélaciens M prof</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" s="2" t="n">
-        <v>4630.237137769792</v>
+        <v>12012.32054538183</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>20216.79169189759</v>
@@ -7192,6 +7195,9 @@
       </c>
       <c r="V40" s="2" t="n">
         <v>38259.64232862164</v>
+      </c>
+      <c r="X40" t="n">
+        <v>4630.237137769792</v>
       </c>
     </row>
     <row r="41">
@@ -7203,11 +7209,8 @@
           <t>Sélaciens L côtiers</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" s="2" t="n">
-        <v>6739.706422802886</v>
+        <v>19687.63058648092</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>40848.67536261171</v>
@@ -7256,6 +7259,9 @@
       </c>
       <c r="V41" s="2" t="n">
         <v>133154.3696116995</v>
+      </c>
+      <c r="X41" t="n">
+        <v>6739.706422802886</v>
       </c>
     </row>
     <row r="42">
@@ -7267,11 +7273,8 @@
           <t>Sélaciens L prof</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" s="2" t="n">
-        <v>8771.288942146815</v>
+        <v>25677.88749629047</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>85025.56939315108</v>
@@ -7320,6 +7323,9 @@
       </c>
       <c r="V42" s="2" t="n">
         <v>623084.0588927014</v>
+      </c>
+      <c r="X42" t="n">
+        <v>8771.288942146815</v>
       </c>
     </row>
     <row r="43">
@@ -7331,11 +7337,8 @@
           <t>Oiseaux</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" s="2" t="n">
-        <v>1772.697544831839</v>
+        <v>4679.583740632866</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>143130.3124254137</v>
@@ -7384,6 +7387,9 @@
       </c>
       <c r="V43" s="2" t="n">
         <v>301620.6787919171</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1772.697544831839</v>
       </c>
     </row>
     <row r="44">
@@ -7395,11 +7401,8 @@
           <t>Tortues</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" s="2" t="n">
-        <v>46.89999889969179</v>
+        <v>76.46930366507489</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>215.5416666666667</v>
@@ -7448,6 +7451,9 @@
       </c>
       <c r="V44" s="2" t="n">
         <v>243.2657790223243</v>
+      </c>
+      <c r="X44" t="n">
+        <v>46.89999889969179</v>
       </c>
     </row>
     <row r="45">
@@ -7459,11 +7465,8 @@
           <t>Dauphins</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" s="2" t="n">
-        <v>6712.57975844763</v>
+        <v>17489.40533891239</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>224810.5537062756</v>
@@ -7512,6 +7515,9 @@
       </c>
       <c r="V45" s="2" t="n">
         <v>456953.901971593</v>
+      </c>
+      <c r="X45" t="n">
+        <v>6712.57975844763</v>
       </c>
     </row>
     <row r="46">
@@ -7523,11 +7529,8 @@
           <t>Baleines</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" s="2" t="n">
-        <v>1875.952811108944</v>
+        <v>5013.174231801515</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>104769.1440951916</v>
@@ -7576,6 +7579,9 @@
       </c>
       <c r="V46" s="2" t="n">
         <v>242908.6687601026</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1875.952811108944</v>
       </c>
     </row>
   </sheetData>
@@ -7589,7 +7595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V46"/>
+  <dimension ref="A1:X46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -7727,6 +7733,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -7776,19 +7792,22 @@
       <c r="O2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7861,6 +7880,12 @@
       <c r="V3" s="2" t="n">
         <v>0.4259477184223214</v>
       </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -7931,6 +7956,12 @@
       <c r="V4" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -7948,10 +7979,10 @@
         <v>10</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>8.209288523194411</v>
+        <v>9.828866651978794</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>8.209288523194413</v>
+        <v>9.828866651978794</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>8.333333333333334</v>
@@ -8000,6 +8031,12 @@
       </c>
       <c r="V5" s="2" t="n">
         <v>7.860853305148327</v>
+      </c>
+      <c r="W5" t="n">
+        <v>8.209288523194411</v>
+      </c>
+      <c r="X5" t="n">
+        <v>8.209288523194413</v>
       </c>
     </row>
     <row r="6">
@@ -8018,10 +8055,10 @@
         <v>62.50551925273969</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>43.8548950532095</v>
+        <v>60.59756357867412</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>54.20794378913904</v>
+        <v>77.31893666705281</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>41.875</v>
@@ -8070,6 +8107,12 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>45.1319016450555</v>
+      </c>
+      <c r="W6" t="n">
+        <v>43.8548950532095</v>
+      </c>
+      <c r="X6" t="n">
+        <v>54.20794378913904</v>
       </c>
     </row>
     <row r="7">
@@ -8088,10 +8131,10 @@
         <v>14.2252931348537</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>11.33053044346818</v>
+        <v>13.94495879530455</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>16.92257218280908</v>
+        <v>22.64895227049952</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>39.05358085096933</v>
@@ -8140,6 +8183,12 @@
       </c>
       <c r="V7" s="2" t="n">
         <v>48.19726778794774</v>
+      </c>
+      <c r="W7" t="n">
+        <v>11.33053044346818</v>
+      </c>
+      <c r="X7" t="n">
+        <v>16.92257218280908</v>
       </c>
     </row>
     <row r="8">
@@ -8158,10 +8207,10 @@
         <v>79.64921965215197</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>54.73445049251632</v>
+        <v>77.07778214260755</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>122.7535678195503</v>
+        <v>199.4203962834444</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>94.91913400504498</v>
@@ -8210,6 +8259,12 @@
       </c>
       <c r="V8" s="2" t="n">
         <v>140.8975049144198</v>
+      </c>
+      <c r="W8" t="n">
+        <v>54.73445049251632</v>
+      </c>
+      <c r="X8" t="n">
+        <v>122.7535678195503</v>
       </c>
     </row>
     <row r="9">
@@ -8228,10 +8283,10 @@
         <v>822.9269279034352</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>462.9466056118962</v>
+        <v>782.5391995118509</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1388.472944248046</v>
+        <v>2911.869334342676</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>776.132507155848</v>
@@ -8280,6 +8335,12 @@
       </c>
       <c r="V9" s="2" t="n">
         <v>1245.599369298057</v>
+      </c>
+      <c r="W9" t="n">
+        <v>462.9466056118966</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1388.472944248046</v>
       </c>
     </row>
     <row r="10">
@@ -8298,10 +8359,10 @@
         <v>162.3748578804658</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>104.9758803494917</v>
+        <v>156.2958706218733</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>177.3704229713044</v>
+        <v>294.9234390555653</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>261.567791843178</v>
@@ -8350,6 +8411,12 @@
       </c>
       <c r="V10" s="2" t="n">
         <v>372.1769891195785</v>
+      </c>
+      <c r="W10" t="n">
+        <v>104.9758803494916</v>
+      </c>
+      <c r="X10" t="n">
+        <v>177.3704229713044</v>
       </c>
     </row>
     <row r="11">
@@ -8368,10 +8435,10 @@
         <v>340.46778348685</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>206.581337207506</v>
+        <v>325.9073622343616</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>455.1141953711017</v>
+        <v>836.5705584262095</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>876.7974117613165</v>
@@ -8420,6 +8487,12 @@
       </c>
       <c r="V11" s="2" t="n">
         <v>1187.940332262086</v>
+      </c>
+      <c r="W11" t="n">
+        <v>206.581337207506</v>
+      </c>
+      <c r="X11" t="n">
+        <v>455.1141953711017</v>
       </c>
     </row>
     <row r="12">
@@ -8438,10 +8511,10 @@
         <v>534.2865972888744</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>311.9026613394916</v>
+        <v>509.7125944635715</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>836.0886987258446</v>
+        <v>1642.875338352503</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>1036.424217762129</v>
@@ -8490,6 +8563,12 @@
       </c>
       <c r="V12" s="2" t="n">
         <v>1480.144923443977</v>
+      </c>
+      <c r="W12" t="n">
+        <v>311.9026613394916</v>
+      </c>
+      <c r="X12" t="n">
+        <v>836.0886987258446</v>
       </c>
     </row>
     <row r="13">
@@ -8508,10 +8587,10 @@
         <v>1106.358886799506</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>606.807500336016</v>
+        <v>1049.72922587958</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>2931.572843801447</v>
+        <v>7084.212360713962</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>3065.622047622472</v>
@@ -8560,6 +8639,12 @@
       </c>
       <c r="V13" s="2" t="n">
         <v>5385.068956264562</v>
+      </c>
+      <c r="W13" t="n">
+        <v>606.807500336016</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2931.572843801447</v>
       </c>
     </row>
     <row r="14">
@@ -8578,10 +8663,10 @@
         <v>142.2529313485369</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>93.01559353126811</v>
+        <v>137.0631404663871</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>138.9222776032636</v>
+        <v>222.6135316737722</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>360.6735868063702</v>
@@ -8630,6 +8715,12 @@
       </c>
       <c r="V14" s="2" t="n">
         <v>450.3766805784952</v>
+      </c>
+      <c r="W14" t="n">
+        <v>93.01559353126811</v>
+      </c>
+      <c r="X14" t="n">
+        <v>138.9222776032636</v>
       </c>
     </row>
     <row r="15">
@@ -8648,10 +8739,10 @@
         <v>562.12162971029</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>326.7269948879465</v>
+        <v>536.0632527459642</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1284.648584372872</v>
+        <v>2736.237230108857</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>1462.241112391934</v>
@@ -8700,6 +8791,12 @@
       </c>
       <c r="V15" s="2" t="n">
         <v>2470.626866590555</v>
+      </c>
+      <c r="W15" t="n">
+        <v>326.7269948879465</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1284.648584372872</v>
       </c>
     </row>
     <row r="16">
@@ -8718,10 +8815,10 @@
         <v>172.485056387309</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>110.9364386108651</v>
+        <v>165.9524010046222</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>283.9769498392468</v>
+        <v>511.3477231528377</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>706.0045778469935</v>
@@ -8770,6 +8867,12 @@
       </c>
       <c r="V16" s="2" t="n">
         <v>945.5745855891123</v>
+      </c>
+      <c r="W16" t="n">
+        <v>110.9364386108651</v>
+      </c>
+      <c r="X16" t="n">
+        <v>283.9769498392468</v>
       </c>
     </row>
     <row r="17">
@@ -8788,10 +8891,10 @@
         <v>865.1960849299834</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>484.6408757605248</v>
+        <v>822.42499164269</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>2412.043437664621</v>
+        <v>5615.443398454736</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>2545.974661684932</v>
@@ -8840,6 +8943,12 @@
       </c>
       <c r="V17" s="2" t="n">
         <v>3752.0189694639</v>
+      </c>
+      <c r="W17" t="n">
+        <v>484.6408757605248</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2412.043437664621</v>
       </c>
     </row>
     <row r="18">
@@ -8858,10 +8967,10 @@
         <v>128.1425436316223</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>84.54261070973034</v>
+        <v>123.5642670281551</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>318.9408270747434</v>
+        <v>594.5405706629227</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>364.9002862575144</v>
@@ -8910,6 +9019,12 @@
       </c>
       <c r="V18" s="2" t="n">
         <v>511.2901281751808</v>
+      </c>
+      <c r="W18" t="n">
+        <v>84.54261070973034</v>
+      </c>
+      <c r="X18" t="n">
+        <v>318.9408270747434</v>
       </c>
     </row>
     <row r="19">
@@ -8928,10 +9043,10 @@
         <v>702.924270026413</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>400.8152072656994</v>
+        <v>669.2163247902042</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>3457.535342195678</v>
+        <v>8905.433089403092</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>6777.560072903272</v>
@@ -8980,6 +9095,12 @@
       </c>
       <c r="V19" s="2" t="n">
         <v>12062.96911240619</v>
+      </c>
+      <c r="W19" t="n">
+        <v>400.8152072656994</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3457.535342195678</v>
       </c>
     </row>
     <row r="20">
@@ -8998,10 +9119,10 @@
         <v>79.51025575737528</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>54.64713223880897</v>
+        <v>76.9443118766352</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>203.0255638625101</v>
+        <v>373.150929325608</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>228.2044129518676</v>
@@ -9050,6 +9171,12 @@
       </c>
       <c r="V20" s="2" t="n">
         <v>316.4557728011578</v>
+      </c>
+      <c r="W20" t="n">
+        <v>54.64713223880897</v>
+      </c>
+      <c r="X20" t="n">
+        <v>203.0255638625101</v>
       </c>
     </row>
     <row r="21">
@@ -9068,10 +9195,10 @@
         <v>672.7076433977323</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>385.0323779513564</v>
+        <v>640.6596923417839</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1049.849703547218</v>
+        <v>2114.174125012883</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>1064.700924855459</v>
@@ -9120,6 +9247,12 @@
       </c>
       <c r="V21" s="2" t="n">
         <v>1524.660266415124</v>
+      </c>
+      <c r="W21" t="n">
+        <v>385.0323779513564</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1049.849703547218</v>
       </c>
     </row>
     <row r="22">
@@ -9138,10 +9271,10 @@
         <v>545.7576958152508</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>318.0197464274169</v>
+        <v>520.5731843592058</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>2089.118751691412</v>
+        <v>4917.189243282608</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>1275.43472506487</v>
@@ -9190,6 +9323,12 @@
       </c>
       <c r="V22" s="2" t="n">
         <v>1944.112617987525</v>
+      </c>
+      <c r="W22" t="n">
+        <v>318.0197464274169</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2089.118751691412</v>
       </c>
     </row>
     <row r="23">
@@ -9208,10 +9347,10 @@
         <v>170.8376086428909</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>109.967259493877</v>
+        <v>164.3791742150771</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>314.2424627618623</v>
+        <v>573.174129209676</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>332.8124512830228</v>
@@ -9260,6 +9399,12 @@
       </c>
       <c r="V23" s="2" t="n">
         <v>447.4519670628269</v>
+      </c>
+      <c r="W23" t="n">
+        <v>109.967259493877</v>
+      </c>
+      <c r="X23" t="n">
+        <v>314.2424627618623</v>
       </c>
     </row>
     <row r="24">
@@ -9278,10 +9423,10 @@
         <v>579.4247536606935</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>335.9103989800871</v>
+        <v>552.4386815194923</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>876.6022585215766</v>
+        <v>1714.024055441366</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>745.9811820865818</v>
@@ -9330,6 +9475,12 @@
       </c>
       <c r="V24" s="2" t="n">
         <v>1074.896674441316</v>
+      </c>
+      <c r="W24" t="n">
+        <v>335.9103989800871</v>
+      </c>
+      <c r="X24" t="n">
+        <v>876.6022585215766</v>
       </c>
     </row>
     <row r="25">
@@ -9348,10 +9499,10 @@
         <v>20.76151027840222</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>16.0094761719834</v>
+        <v>20.29476542896715</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>63.98476752740117</v>
+        <v>104.0554169221973</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>84.96705299068371</v>
@@ -9400,6 +9551,12 @@
       </c>
       <c r="V25" s="2" t="n">
         <v>89.98594557901284</v>
+      </c>
+      <c r="W25" t="n">
+        <v>16.0094761719834</v>
+      </c>
+      <c r="X25" t="n">
+        <v>63.98476752740117</v>
       </c>
     </row>
     <row r="26">
@@ -9418,10 +9575,10 @@
         <v>207.0661689676665</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>131.1086599435007</v>
+        <v>198.9510815059404</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>435.0675248555729</v>
+        <v>810.5587101098325</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>761.6642352804706</v>
@@ -9470,6 +9627,12 @@
       </c>
       <c r="V26" s="2" t="n">
         <v>1031.42509065577</v>
+      </c>
+      <c r="W26" t="n">
+        <v>131.1086599435007</v>
+      </c>
+      <c r="X26" t="n">
+        <v>435.0675248555729</v>
       </c>
     </row>
     <row r="27">
@@ -9488,10 +9651,10 @@
         <v>446.273553235535</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>264.5726558565414</v>
+        <v>426.3225106096644</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>1050.612043409047</v>
+        <v>2287.410538578006</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>1227.270659320284</v>
@@ -9540,6 +9703,12 @@
       </c>
       <c r="V27" s="2" t="n">
         <v>1742.087801781186</v>
+      </c>
+      <c r="W27" t="n">
+        <v>264.5726558565414</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1050.612043409047</v>
       </c>
     </row>
     <row r="28">
@@ -9558,10 +9727,10 @@
         <v>369.6444639262777</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>222.7097718346612</v>
+        <v>353.6182460448491</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>2268.135359900746</v>
+        <v>5618.010617278358</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>4122.619468921102</v>
@@ -9610,6 +9779,12 @@
       </c>
       <c r="V28" s="2" t="n">
         <v>5978.972399413969</v>
+      </c>
+      <c r="W28" t="n">
+        <v>222.7097718346615</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2268.135359900746</v>
       </c>
     </row>
     <row r="29">
@@ -9628,10 +9803,10 @@
         <v>834.7927019690036</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>469.046046704943</v>
+        <v>793.7374342020636</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>2908.693588357198</v>
+        <v>7076.924212017076</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>5090.678261352627</v>
@@ -9680,6 +9855,12 @@
       </c>
       <c r="V29" s="2" t="n">
         <v>20789.96132187671</v>
+      </c>
+      <c r="W29" t="n">
+        <v>469.0460467049435</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2908.693588357198</v>
       </c>
     </row>
     <row r="30">
@@ -9698,10 +9879,10 @@
         <v>1068.453681872593</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>587.7708639076791</v>
+        <v>1014.029198214386</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>3503.550698579406</v>
+        <v>8964.713936525101</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>3381.078685869309</v>
@@ -9750,6 +9931,12 @@
       </c>
       <c r="V30" s="2" t="n">
         <v>4954.168964716645</v>
+      </c>
+      <c r="W30" t="n">
+        <v>587.7708639076791</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3503.550698579406</v>
       </c>
     </row>
     <row r="31">
@@ -9768,10 +9955,10 @@
         <v>765.126207506748</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>433.1248187812554</v>
+        <v>727.9725586500032</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>1494.308190619101</v>
+        <v>3298.256219855545</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>1392.358439628146</v>
@@ -9820,6 +10007,12 @@
       </c>
       <c r="V31" s="2" t="n">
         <v>3084.901189558607</v>
+      </c>
+      <c r="W31" t="n">
+        <v>433.1248187812554</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1494.308190619101</v>
       </c>
     </row>
     <row r="32">
@@ -9838,10 +10031,10 @@
         <v>157.9708642772723</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>102.3696176359204</v>
+        <v>152.0881007631247</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>312.7900125953055</v>
+        <v>577.2716612337013</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>239.8102363777903</v>
@@ -9890,6 +10083,12 @@
       </c>
       <c r="V32" s="2" t="n">
         <v>339.6228389540004</v>
+      </c>
+      <c r="W32" t="n">
+        <v>102.3696176359204</v>
+      </c>
+      <c r="X32" t="n">
+        <v>312.7900125953055</v>
       </c>
     </row>
     <row r="33">
@@ -9908,10 +10107,10 @@
         <v>1087.886765379727</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>597.5375907232642</v>
+        <v>1032.332905842053</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>2190.295135872755</v>
+        <v>5007.056465627202</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>3058.864857863693</v>
@@ -9960,6 +10159,12 @@
       </c>
       <c r="V33" s="2" t="n">
         <v>6096.553542412496</v>
+      </c>
+      <c r="W33" t="n">
+        <v>597.5375907232642</v>
+      </c>
+      <c r="X33" t="n">
+        <v>2190.295135872755</v>
       </c>
     </row>
     <row r="34">
@@ -9978,10 +10183,10 @@
         <v>32.7571509830473</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>24.29141153387523</v>
+        <v>31.9114504099423</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>44.95383924474417</v>
+        <v>65.81843435831895</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>85.31188989228311</v>
@@ -10030,6 +10235,12 @@
       </c>
       <c r="V34" s="2" t="n">
         <v>95.67255553115217</v>
+      </c>
+      <c r="W34" t="n">
+        <v>24.29141153387523</v>
+      </c>
+      <c r="X34" t="n">
+        <v>44.95383924474417</v>
       </c>
     </row>
     <row r="35">
@@ -10048,10 +10259,10 @@
         <v>63.3717833988014</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>44.4102679807413</v>
+        <v>61.43104649112051</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>180.2821286627297</v>
+        <v>318.7090445260008</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>117.8712625973944</v>
@@ -10100,6 +10311,12 @@
       </c>
       <c r="V35" s="2" t="n">
         <v>189.6907153599787</v>
+      </c>
+      <c r="W35" t="n">
+        <v>44.4102679807413</v>
+      </c>
+      <c r="X35" t="n">
+        <v>180.2821286627297</v>
       </c>
     </row>
     <row r="36">
@@ -10118,10 +10335,10 @@
         <v>1052.557932833487</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>579.7706251423608</v>
+        <v>999.0553950676908</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>4535.503078268507</v>
+        <v>11777.34538378649</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>6532.702987739271</v>
@@ -10170,6 +10387,12 @@
       </c>
       <c r="V36" s="2" t="n">
         <v>15274.19021141982</v>
+      </c>
+      <c r="W36" t="n">
+        <v>579.7706251423608</v>
+      </c>
+      <c r="X36" t="n">
+        <v>4535.503078268507</v>
       </c>
     </row>
     <row r="37">
@@ -10188,10 +10411,10 @@
         <v>1395.634936826377</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>750.3817179249652</v>
+        <v>1321.89473070454</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>3860.200613202962</v>
+        <v>9241.370942749292</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>2965.06417411219</v>
@@ -10240,6 +10463,12 @@
       </c>
       <c r="V37" s="2" t="n">
         <v>4550.070821322682</v>
+      </c>
+      <c r="W37" t="n">
+        <v>750.3817179249652</v>
+      </c>
+      <c r="X37" t="n">
+        <v>3860.200613202962</v>
       </c>
     </row>
     <row r="38">
@@ -10258,10 +10487,10 @@
         <v>2736.422784933652</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>1388.786767442071</v>
+        <v>2578.791074077171</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>6982.23243364418</v>
+        <v>17894.30232400511</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>8524.622237620406</v>
@@ -10310,6 +10539,12 @@
       </c>
       <c r="V38" s="2" t="n">
         <v>14860.28288827575</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1388.786767442071</v>
+      </c>
+      <c r="X38" t="n">
+        <v>6982.23243364418</v>
       </c>
     </row>
     <row r="39">
@@ -10328,10 +10563,10 @@
         <v>1208.786277417204</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>657.9746784948589</v>
+        <v>1146.15278058636</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>4429.141123038974</v>
+        <v>11499.00467731808</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>16016.71794153378</v>
@@ -10380,6 +10615,12 @@
       </c>
       <c r="V39" s="2" t="n">
         <v>30078.7151971144</v>
+      </c>
+      <c r="W39" t="n">
+        <v>657.9746784948589</v>
+      </c>
+      <c r="X39" t="n">
+        <v>4429.141123038974</v>
       </c>
     </row>
     <row r="40">
@@ -10398,10 +10639,10 @@
         <v>2768.400810266461</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>1403.618051665464</v>
+        <v>2608.699783624969</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>6258.766097198265</v>
+        <v>15804.75226272186</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>29649.13370640371</v>
@@ -10450,6 +10691,12 @@
       </c>
       <c r="V40" s="2" t="n">
         <v>47003.1815902428</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1403.618051665464</v>
+      </c>
+      <c r="X40" t="n">
+        <v>6258.766097198265</v>
       </c>
     </row>
     <row r="41">
@@ -10468,10 +10715,10 @@
         <v>1149.132986700125</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>628.2224463747292</v>
+        <v>1090.003898831064</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>9214.946091355934</v>
+        <v>26127.27035224584</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>60049.46083251206</v>
@@ -10520,6 +10767,12 @@
       </c>
       <c r="V41" s="2" t="n">
         <v>163593.2508741701</v>
+      </c>
+      <c r="W41" t="n">
+        <v>628.222446374728</v>
+      </c>
+      <c r="X41" t="n">
+        <v>9214.946091355934</v>
       </c>
     </row>
     <row r="42">
@@ -10538,10 +10791,10 @@
         <v>2984.35669373795</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>1503.402269971377</v>
+        <v>2810.614696808107</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>11832.43810189137</v>
+        <v>33755.93780144437</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>124488.4155412689</v>
@@ -10590,6 +10843,12 @@
       </c>
       <c r="V42" s="2" t="n">
         <v>764649.1711995355</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1503.402269971377</v>
+      </c>
+      <c r="X42" t="n">
+        <v>11832.43810189137</v>
       </c>
     </row>
     <row r="43">
@@ -10608,10 +10867,10 @@
         <v>331.2899800085807</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>201.4839052302981</v>
+        <v>317.1870265007098</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>2385.08479507897</v>
+        <v>6140.787560856473</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>209862.3797595799</v>
@@ -10660,6 +10919,12 @@
       </c>
       <c r="V43" s="2" t="n">
         <v>370142.7189656865</v>
+      </c>
+      <c r="W43" t="n">
+        <v>201.4839052302981</v>
+      </c>
+      <c r="X43" t="n">
+        <v>2385.08479507897</v>
       </c>
     </row>
     <row r="44">
@@ -10678,10 +10943,10 @@
         <v>15.1213942542505</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>11.9813933751079</v>
+        <v>14.81661374364027</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>51.88922475228967</v>
+        <v>84.8417318041065</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>237.4166666666667</v>
@@ -10730,6 +10995,12 @@
       </c>
       <c r="V44" s="2" t="n">
         <v>254.0608779579962</v>
+      </c>
+      <c r="W44" t="n">
+        <v>11.9813933751079</v>
+      </c>
+      <c r="X44" t="n">
+        <v>51.88922475228967</v>
       </c>
     </row>
     <row r="45">
@@ -10748,10 +11019,10 @@
         <v>4539.216283629031</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>2205.960849341395</v>
+        <v>4261.535503639439</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>9097.444698178908</v>
+        <v>23034.65403955883</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>327272.0772808701</v>
@@ -10800,6 +11071,12 @@
       </c>
       <c r="V45" s="2" t="n">
         <v>559821.9794233225</v>
+      </c>
+      <c r="W45" t="n">
+        <v>2205.960849341395</v>
+      </c>
+      <c r="X45" t="n">
+        <v>9097.444698178908</v>
       </c>
     </row>
     <row r="46">
@@ -10818,10 +11095,10 @@
         <v>901.6702172121619</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>503.2878494050452</v>
+        <v>856.8307444671187</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>2450.852110731608</v>
+        <v>6476.556939926386</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>149657.6713846845</v>
@@ -10870,6 +11147,12 @@
       </c>
       <c r="V46" s="2" t="n">
         <v>295987.2470950339</v>
+      </c>
+      <c r="W46" t="n">
+        <v>503.2878494050448</v>
+      </c>
+      <c r="X46" t="n">
+        <v>2450.852110731608</v>
       </c>
     </row>
   </sheetData>
@@ -10883,7 +11166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V46"/>
+  <dimension ref="A1:X46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -11021,6 +11304,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -11070,19 +11363,22 @@
       <c r="O2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11155,6 +11451,12 @@
       <c r="V3" s="2" t="n">
         <v>0.4259477184223214</v>
       </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -11225,6 +11527,12 @@
       <c r="V4" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -11242,10 +11550,10 @@
         <v>10</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>8.209288523194411</v>
+        <v>9.828866651978794</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>8.209288523194413</v>
+        <v>9.828866651978794</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>8.333333333333334</v>
@@ -11294,6 +11602,12 @@
       </c>
       <c r="V5" s="2" t="n">
         <v>7.860853305148327</v>
+      </c>
+      <c r="W5" t="n">
+        <v>8.209288523194411</v>
+      </c>
+      <c r="X5" t="n">
+        <v>8.209288523194413</v>
       </c>
     </row>
     <row r="6">
@@ -11312,10 +11626,10 @@
         <v>62.50551925273969</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>43.8548950532095</v>
+        <v>60.59756357867412</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>54.20794378913904</v>
+        <v>77.31893666705281</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>41.875</v>
@@ -11364,6 +11678,12 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>45.1319016450555</v>
+      </c>
+      <c r="W6" t="n">
+        <v>43.8548950532095</v>
+      </c>
+      <c r="X6" t="n">
+        <v>54.20794378913904</v>
       </c>
     </row>
     <row r="7">
@@ -11382,10 +11702,10 @@
         <v>14.2252931348537</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>11.33053044346818</v>
+        <v>13.94495879530455</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>16.92257218280908</v>
+        <v>22.64895227049952</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>39.05358085096933</v>
@@ -11434,6 +11754,12 @@
       </c>
       <c r="V7" s="2" t="n">
         <v>48.19726778794774</v>
+      </c>
+      <c r="W7" t="n">
+        <v>11.33053044346818</v>
+      </c>
+      <c r="X7" t="n">
+        <v>16.92257218280908</v>
       </c>
     </row>
     <row r="8">
@@ -11452,10 +11778,10 @@
         <v>79.64921965215197</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>54.73445049251632</v>
+        <v>77.07778214260755</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>122.7535678195503</v>
+        <v>199.4203962834444</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>94.91913400504498</v>
@@ -11504,6 +11830,12 @@
       </c>
       <c r="V8" s="2" t="n">
         <v>140.8975049144198</v>
+      </c>
+      <c r="W8" t="n">
+        <v>54.73445049251632</v>
+      </c>
+      <c r="X8" t="n">
+        <v>122.7535678195503</v>
       </c>
     </row>
     <row r="9">
@@ -11522,10 +11854,10 @@
         <v>822.9269279034352</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>462.9466056118962</v>
+        <v>782.5391995118509</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1388.475780645967</v>
+        <v>2911.873630476624</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>776.1337460874031</v>
@@ -11574,6 +11906,12 @@
       </c>
       <c r="V9" s="2" t="n">
         <v>1245.601022174115</v>
+      </c>
+      <c r="W9" t="n">
+        <v>462.9466056118966</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1388.475780645967</v>
       </c>
     </row>
     <row r="10">
@@ -11592,10 +11930,10 @@
         <v>162.3748578804658</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>104.9758803494917</v>
+        <v>156.2958706218733</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>177.3704229713044</v>
+        <v>294.9234390555653</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>261.567791843178</v>
@@ -11644,6 +11982,12 @@
       </c>
       <c r="V10" s="2" t="n">
         <v>372.1770603168501</v>
+      </c>
+      <c r="W10" t="n">
+        <v>104.9758803494916</v>
+      </c>
+      <c r="X10" t="n">
+        <v>177.3704229713044</v>
       </c>
     </row>
     <row r="11">
@@ -11662,10 +12006,10 @@
         <v>340.46778348685</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>206.581337207506</v>
+        <v>325.9073622343616</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>455.1141953711017</v>
+        <v>836.5705584262095</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>876.7974117613165</v>
@@ -11714,6 +12058,12 @@
       </c>
       <c r="V11" s="2" t="n">
         <v>1187.940441684514</v>
+      </c>
+      <c r="W11" t="n">
+        <v>206.581337207506</v>
+      </c>
+      <c r="X11" t="n">
+        <v>455.1141953711017</v>
       </c>
     </row>
     <row r="12">
@@ -11732,10 +12082,10 @@
         <v>534.2865972888744</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>311.9026613394916</v>
+        <v>509.7125944635715</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>836.0886987258446</v>
+        <v>1642.875338352503</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>1036.424217762129</v>
@@ -11784,6 +12134,12 @@
       </c>
       <c r="V12" s="2" t="n">
         <v>1480.145124117653</v>
+      </c>
+      <c r="W12" t="n">
+        <v>311.9026613394916</v>
+      </c>
+      <c r="X12" t="n">
+        <v>836.0886987258446</v>
       </c>
     </row>
     <row r="13">
@@ -11802,10 +12158,10 @@
         <v>1106.358886799506</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>606.807500336016</v>
+        <v>1049.72922587958</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>2931.579205286321</v>
+        <v>7084.224773525888</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>3065.630109529245</v>
@@ -11854,6 +12210,12 @@
       </c>
       <c r="V13" s="2" t="n">
         <v>5385.081532208244</v>
+      </c>
+      <c r="W13" t="n">
+        <v>606.807500336016</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2931.579205286321</v>
       </c>
     </row>
     <row r="14">
@@ -11872,10 +12234,10 @@
         <v>142.2529313485369</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>93.01559353126811</v>
+        <v>137.0631404663871</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>138.9222776032636</v>
+        <v>222.6135316737722</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>360.6735868063702</v>
@@ -11924,6 +12286,12 @@
       </c>
       <c r="V14" s="2" t="n">
         <v>450.3766805784952</v>
+      </c>
+      <c r="W14" t="n">
+        <v>93.01559353126811</v>
+      </c>
+      <c r="X14" t="n">
+        <v>138.9222776032636</v>
       </c>
     </row>
     <row r="15">
@@ -11942,10 +12310,10 @@
         <v>562.12162971029</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>326.7269948879465</v>
+        <v>536.0632527459642</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>1284.662742444876</v>
+        <v>2736.257525618601</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>1462.2512512582</v>
@@ -11994,6 +12362,12 @@
       </c>
       <c r="V15" s="2" t="n">
         <v>2470.640553309572</v>
+      </c>
+      <c r="W15" t="n">
+        <v>326.7269948879465</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1284.662742444876</v>
       </c>
     </row>
     <row r="16">
@@ -12012,10 +12386,10 @@
         <v>172.485056387309</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>110.9364386108651</v>
+        <v>165.9524010046222</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>283.9769498392468</v>
+        <v>511.3477231528377</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>706.0045778469935</v>
@@ -12064,6 +12438,12 @@
       </c>
       <c r="V16" s="2" t="n">
         <v>945.5745855891123</v>
+      </c>
+      <c r="W16" t="n">
+        <v>110.9364386108651</v>
+      </c>
+      <c r="X16" t="n">
+        <v>283.9769498392468</v>
       </c>
     </row>
     <row r="17">
@@ -12082,10 +12462,10 @@
         <v>865.1960849299834</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>484.6408757605248</v>
+        <v>822.42499164269</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>2412.077537356979</v>
+        <v>5615.493406904687</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>2546.01171127614</v>
@@ -12134,6 +12514,12 @@
       </c>
       <c r="V17" s="2" t="n">
         <v>3752.059359788516</v>
+      </c>
+      <c r="W17" t="n">
+        <v>484.6408757605248</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2412.077537356979</v>
       </c>
     </row>
     <row r="18">
@@ -12152,10 +12538,10 @@
         <v>128.1425436316223</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>84.54261070973034</v>
+        <v>123.5642670281551</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>318.9408270747434</v>
+        <v>594.5405706629227</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>364.9002862575144</v>
@@ -12204,6 +12590,12 @@
       </c>
       <c r="V18" s="2" t="n">
         <v>511.2901281751808</v>
+      </c>
+      <c r="W18" t="n">
+        <v>84.54261070973034</v>
+      </c>
+      <c r="X18" t="n">
+        <v>318.9408270747434</v>
       </c>
     </row>
     <row r="19">
@@ -12222,10 +12614,10 @@
         <v>702.924270026413</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>400.8152072656994</v>
+        <v>669.2163247902042</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>3457.57161770575</v>
+        <v>8905.495620979342</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>6777.626749028872</v>
@@ -12274,6 +12666,12 @@
       </c>
       <c r="V19" s="2" t="n">
         <v>12063.0585809616</v>
+      </c>
+      <c r="W19" t="n">
+        <v>400.8152072656994</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3457.57161770575</v>
       </c>
     </row>
     <row r="20">
@@ -12292,10 +12690,10 @@
         <v>79.51025575737528</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>54.64713223880897</v>
+        <v>76.9443118766352</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>203.0501917284947</v>
+        <v>373.1804159260608</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>228.2267296696607</v>
@@ -12344,6 +12742,12 @@
       </c>
       <c r="V20" s="2" t="n">
         <v>316.4796075179043</v>
+      </c>
+      <c r="W20" t="n">
+        <v>54.64713223880897</v>
+      </c>
+      <c r="X20" t="n">
+        <v>203.0501917284947</v>
       </c>
     </row>
     <row r="21">
@@ -12362,10 +12766,10 @@
         <v>672.7076433977323</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>385.0323779513564</v>
+        <v>640.6596923417839</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1049.869914535125</v>
+        <v>2114.203097340603</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>1064.720980067211</v>
@@ -12414,6 +12818,12 @@
       </c>
       <c r="V21" s="2" t="n">
         <v>1524.681824908291</v>
+      </c>
+      <c r="W21" t="n">
+        <v>385.0323779513564</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1049.869914535125</v>
       </c>
     </row>
     <row r="22">
@@ -12432,10 +12842,10 @@
         <v>545.7576958152508</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>318.0197464274169</v>
+        <v>520.5731843592058</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>2089.141318415112</v>
+        <v>4917.222698480244</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>1275.451871372594</v>
@@ -12484,6 +12894,12 @@
       </c>
       <c r="V22" s="2" t="n">
         <v>1944.131304242527</v>
+      </c>
+      <c r="W22" t="n">
+        <v>318.0197464274169</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2089.141318415112</v>
       </c>
     </row>
     <row r="23">
@@ -12502,10 +12918,10 @@
         <v>170.8376086428909</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>109.967259493877</v>
+        <v>164.3791742150771</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>314.2424627618623</v>
+        <v>573.174129209676</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>332.8124512830228</v>
@@ -12554,6 +12970,12 @@
       </c>
       <c r="V23" s="2" t="n">
         <v>447.4519670628269</v>
+      </c>
+      <c r="W23" t="n">
+        <v>109.967259493877</v>
+      </c>
+      <c r="X23" t="n">
+        <v>314.2424627618623</v>
       </c>
     </row>
     <row r="24">
@@ -12572,10 +12994,10 @@
         <v>579.4247536606935</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>335.9103989800871</v>
+        <v>552.4386815194923</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>876.6078745565205</v>
+        <v>1714.032105993156</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>745.9863385738781</v>
@@ -12624,6 +13046,12 @@
       </c>
       <c r="V24" s="2" t="n">
         <v>1074.902147437991</v>
+      </c>
+      <c r="W24" t="n">
+        <v>335.9103989800871</v>
+      </c>
+      <c r="X24" t="n">
+        <v>876.6078745565205</v>
       </c>
     </row>
     <row r="25">
@@ -12642,10 +13070,10 @@
         <v>20.76151027840222</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>16.0094761719834</v>
+        <v>20.29476542896715</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>63.98476752740117</v>
+        <v>104.0554169221973</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>84.96705299068371</v>
@@ -12694,6 +13122,12 @@
       </c>
       <c r="V25" s="2" t="n">
         <v>89.98594557901284</v>
+      </c>
+      <c r="W25" t="n">
+        <v>16.0094761719834</v>
+      </c>
+      <c r="X25" t="n">
+        <v>63.98476752740117</v>
       </c>
     </row>
     <row r="26">
@@ -12712,10 +13146,10 @@
         <v>207.0661689676665</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>131.1086599435007</v>
+        <v>198.9510815059404</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>435.0675248555729</v>
+        <v>810.5587101098325</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>761.6642352804706</v>
@@ -12764,6 +13198,12 @@
       </c>
       <c r="V26" s="2" t="n">
         <v>1031.42509065577</v>
+      </c>
+      <c r="W26" t="n">
+        <v>131.1086599435007</v>
+      </c>
+      <c r="X26" t="n">
+        <v>435.0675248555729</v>
       </c>
     </row>
     <row r="27">
@@ -12782,10 +13222,10 @@
         <v>446.273553235535</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>264.5726558565414</v>
+        <v>426.3225106096644</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>1050.626857398079</v>
+        <v>2287.433384793238</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>1227.287783652643</v>
@@ -12834,6 +13274,12 @@
       </c>
       <c r="V27" s="2" t="n">
         <v>1742.10620191493</v>
+      </c>
+      <c r="W27" t="n">
+        <v>264.5726558565414</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1050.626857398079</v>
       </c>
     </row>
     <row r="28">
@@ -12852,10 +13298,10 @@
         <v>369.6444639262777</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>222.7097718346612</v>
+        <v>353.6182460448491</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>2268.177034202288</v>
+        <v>5618.07675978808</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>4122.703208317054</v>
@@ -12904,6 +13350,12 @@
       </c>
       <c r="V28" s="2" t="n">
         <v>5979.06236232317</v>
+      </c>
+      <c r="W28" t="n">
+        <v>222.7097718346615</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2268.177034202288</v>
       </c>
     </row>
     <row r="29">
@@ -12922,10 +13374,10 @@
         <v>834.7927019690036</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>469.046046704943</v>
+        <v>793.7374342020636</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>2908.726875449176</v>
+        <v>7076.977860276024</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>5090.744395739151</v>
@@ -12974,6 +13426,12 @@
       </c>
       <c r="V29" s="2" t="n">
         <v>20790.11571925702</v>
+      </c>
+      <c r="W29" t="n">
+        <v>469.0460467049435</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2908.726875449176</v>
       </c>
     </row>
     <row r="30">
@@ -12992,10 +13450,10 @@
         <v>1068.453681872593</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>587.7708639076791</v>
+        <v>1014.029198214386</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>3503.61011456388</v>
+        <v>8964.81745390745</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>3381.137464955041</v>
@@ -13044,6 +13502,12 @@
       </c>
       <c r="V30" s="2" t="n">
         <v>4954.233598999737</v>
+      </c>
+      <c r="W30" t="n">
+        <v>587.7708639076791</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3503.61011456388</v>
       </c>
     </row>
     <row r="31">
@@ -13062,10 +13526,10 @@
         <v>765.126207506748</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>433.1248187812554</v>
+        <v>727.9725586500032</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>1494.315019840296</v>
+        <v>3298.268004205671</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>1392.3666182353</v>
@@ -13114,6 +13578,12 @@
       </c>
       <c r="V31" s="2" t="n">
         <v>3084.917054187977</v>
+      </c>
+      <c r="W31" t="n">
+        <v>433.1248187812554</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1494.315019840296</v>
       </c>
     </row>
     <row r="32">
@@ -13132,10 +13602,10 @@
         <v>157.9708642772723</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>102.3696176359204</v>
+        <v>152.0881007631247</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>312.7900125953055</v>
+        <v>577.2716612337013</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>239.8102363777903</v>
@@ -13184,6 +13654,12 @@
       </c>
       <c r="V32" s="2" t="n">
         <v>339.6228820649721</v>
+      </c>
+      <c r="W32" t="n">
+        <v>102.3696176359204</v>
+      </c>
+      <c r="X32" t="n">
+        <v>312.7900125953055</v>
       </c>
     </row>
     <row r="33">
@@ -13202,10 +13678,10 @@
         <v>1087.886765379727</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>597.5375907232642</v>
+        <v>1032.332905842053</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>2190.300013502349</v>
+        <v>5007.066640212674</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>3058.87129434545</v>
@@ -13254,6 +13730,12 @@
       </c>
       <c r="V33" s="2" t="n">
         <v>6096.563991926266</v>
+      </c>
+      <c r="W33" t="n">
+        <v>597.5375907232642</v>
+      </c>
+      <c r="X33" t="n">
+        <v>2190.300013502349</v>
       </c>
     </row>
     <row r="34">
@@ -13272,10 +13754,10 @@
         <v>32.7571509830473</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>24.29141153387523</v>
+        <v>31.9114504099423</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>44.95383924474417</v>
+        <v>65.81843435831895</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>85.31188989228311</v>
@@ -13324,6 +13806,12 @@
       </c>
       <c r="V34" s="2" t="n">
         <v>95.67255553115217</v>
+      </c>
+      <c r="W34" t="n">
+        <v>24.29141153387523</v>
+      </c>
+      <c r="X34" t="n">
+        <v>44.95383924474417</v>
       </c>
     </row>
     <row r="35">
@@ -13342,10 +13830,10 @@
         <v>63.3717833988014</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>44.4102679807413</v>
+        <v>61.43104649112051</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>180.2821286627297</v>
+        <v>318.7090445260008</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>117.8712625973944</v>
@@ -13394,6 +13882,12 @@
       </c>
       <c r="V35" s="2" t="n">
         <v>189.6907167790037</v>
+      </c>
+      <c r="W35" t="n">
+        <v>44.4102679807413</v>
+      </c>
+      <c r="X35" t="n">
+        <v>180.2821286627297</v>
       </c>
     </row>
     <row r="36">
@@ -13412,10 +13906,10 @@
         <v>1052.557932833487</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>579.7706251423608</v>
+        <v>999.0553950676908</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>4535.549158253944</v>
+        <v>11777.42352255806</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>6532.776467534154</v>
@@ -13464,6 +13958,12 @@
       </c>
       <c r="V36" s="2" t="n">
         <v>15274.30670656247</v>
+      </c>
+      <c r="W36" t="n">
+        <v>579.7706251423608</v>
+      </c>
+      <c r="X36" t="n">
+        <v>4535.549158253944</v>
       </c>
     </row>
     <row r="37">
@@ -13482,10 +13982,10 @@
         <v>1395.634936826377</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>750.3817179249652</v>
+        <v>1321.89473070454</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>3860.227378085896</v>
+        <v>9241.412089599642</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>2965.086478591566</v>
@@ -13534,6 +14034,12 @@
       </c>
       <c r="V37" s="2" t="n">
         <v>4550.096146409545</v>
+      </c>
+      <c r="W37" t="n">
+        <v>750.3817179249652</v>
+      </c>
+      <c r="X37" t="n">
+        <v>3860.227378085896</v>
       </c>
     </row>
     <row r="38">
@@ -13552,10 +14058,10 @@
         <v>2736.422784933652</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>1388.786767442071</v>
+        <v>2578.791074077171</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>6982.262246401046</v>
+        <v>17894.35785570653</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>8524.661732389577</v>
@@ -13604,6 +14110,12 @@
       </c>
       <c r="V38" s="2" t="n">
         <v>14860.33632780813</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1388.786767442071</v>
+      </c>
+      <c r="X38" t="n">
+        <v>6982.262246401046</v>
       </c>
     </row>
     <row r="39">
@@ -13622,10 +14134,10 @@
         <v>1208.786277417204</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>657.9746784948589</v>
+        <v>1146.15278058636</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>4429.175462727982</v>
+        <v>11499.06532182326</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>16016.84393574997</v>
@@ -13674,6 +14186,12 @@
       </c>
       <c r="V39" s="2" t="n">
         <v>30078.89094918133</v>
+      </c>
+      <c r="W39" t="n">
+        <v>657.9746784948589</v>
+      </c>
+      <c r="X39" t="n">
+        <v>4429.175462727982</v>
       </c>
     </row>
     <row r="40">
@@ -13692,10 +14210,10 @@
         <v>2768.400810266461</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>1403.618051665464</v>
+        <v>2608.699783624969</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>6258.794186667383</v>
+        <v>15804.80239791436</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>29649.25921897545</v>
@@ -13744,6 +14262,12 @@
       </c>
       <c r="V40" s="2" t="n">
         <v>47003.34151131392</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1403.618051665464</v>
+      </c>
+      <c r="X40" t="n">
+        <v>6258.794186667383</v>
       </c>
     </row>
     <row r="41">
@@ -13762,10 +14286,10 @@
         <v>1149.132986700125</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>628.2224463747292</v>
+        <v>1090.003898831064</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>9215.010266242958</v>
+        <v>26127.3955661533</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>60050.07500886762</v>
@@ -13814,6 +14338,12 @@
       </c>
       <c r="V41" s="2" t="n">
         <v>163594.2759401503</v>
+      </c>
+      <c r="W41" t="n">
+        <v>628.222446374728</v>
+      </c>
+      <c r="X41" t="n">
+        <v>9215.010266242958</v>
       </c>
     </row>
     <row r="42">
@@ -13832,10 +14362,10 @@
         <v>2984.35669373795</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>1503.402269971377</v>
+        <v>2810.614696808107</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>11832.50558864843</v>
+        <v>33756.07582738178</v>
       </c>
       <c r="G42" s="2" t="n">
         <v>124489.0688351706</v>
@@ -13884,6 +14414,12 @@
       </c>
       <c r="V42" s="2" t="n">
         <v>764652.412024294</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1503.402269971377</v>
+      </c>
+      <c r="X42" t="n">
+        <v>11832.50558864843</v>
       </c>
     </row>
     <row r="43">
@@ -13902,10 +14438,10 @@
         <v>331.2899800085807</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>201.4839052302981</v>
+        <v>317.1870265007098</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>2386.159487092681</v>
+        <v>6142.085341602322</v>
       </c>
       <c r="G43" s="2" t="n">
         <v>209966.3824372252</v>
@@ -13954,6 +14490,12 @@
       </c>
       <c r="V43" s="2" t="n">
         <v>370247.5739143033</v>
+      </c>
+      <c r="W43" t="n">
+        <v>201.4839052302981</v>
+      </c>
+      <c r="X43" t="n">
+        <v>2386.159487092681</v>
       </c>
     </row>
     <row r="44">
@@ -13972,10 +14514,10 @@
         <v>15.1213942542505</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>11.9813933751079</v>
+        <v>14.81661374364027</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>51.88922475228967</v>
+        <v>84.8417318041065</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>237.4166666666667</v>
@@ -14024,6 +14566,12 @@
       </c>
       <c r="V44" s="2" t="n">
         <v>254.0608779579962</v>
+      </c>
+      <c r="W44" t="n">
+        <v>11.9813933751079</v>
+      </c>
+      <c r="X44" t="n">
+        <v>51.88922475228967</v>
       </c>
     </row>
     <row r="45">
@@ -14042,10 +14590,10 @@
         <v>4539.216283629031</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>2205.960849341395</v>
+        <v>4261.535503639439</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>9097.473580978283</v>
+        <v>23034.70589380794</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>327273.2462400916</v>
@@ -14094,6 +14642,12 @@
       </c>
       <c r="V45" s="2" t="n">
         <v>559823.6405459424</v>
+      </c>
+      <c r="W45" t="n">
+        <v>2205.960849341395</v>
+      </c>
+      <c r="X45" t="n">
+        <v>9097.473580978283</v>
       </c>
     </row>
     <row r="46">
@@ -14112,10 +14666,10 @@
         <v>901.6702172121619</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>503.2878494050452</v>
+        <v>856.8307444671187</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>2450.865465566402</v>
+        <v>6476.583862107371</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>149658.7284059021</v>
@@ -14164,6 +14718,12 @@
       </c>
       <c r="V46" s="2" t="n">
         <v>295988.9330012708</v>
+      </c>
+      <c r="W46" t="n">
+        <v>503.2878494050448</v>
+      </c>
+      <c r="X46" t="n">
+        <v>2450.865465566402</v>
       </c>
     </row>
   </sheetData>
@@ -14635,7 +15195,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
       <c r="AD2" s="2" t="n">
         <v>0.354813494722674</v>
       </c>
@@ -14761,7 +15320,6 @@
       <c r="H3" t="b">
         <v>0</v>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Guinea (1998)</t>
@@ -14825,7 +15383,6 @@
           <t>WARN</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
       <c r="AD3" s="2" t="n">
         <v>0</v>
       </c>
@@ -15019,7 +15576,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
       <c r="AD4" s="2" t="n">
         <v>0.4341351991679275</v>
       </c>
@@ -15121,7 +15677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -15182,14 +15738,12 @@
       <c r="C2" s="2" t="n">
         <v>142.1408557234829</v>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" s="2" t="n">
         <v>4116</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0.03453373559851382</v>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -15203,14 +15757,12 @@
       <c r="C3" s="2" t="n">
         <v>312.4564218823575</v>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" s="2" t="n">
         <v>4116</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0.0759126389412919</v>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -15219,19 +15771,17 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>180.0914572727739</v>
+        <v>297.68656332722</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>180.0914572727739</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>297.68656332722</v>
+      </c>
       <c r="E4" s="2" t="n">
         <v>4116</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.04375399836559134</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
+        <v>0.07232423793178329</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -15240,22 +15790,22 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>804.8811474593635</v>
+        <v>1880.595800294457</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>804.8753435154925</v>
+        <v>1880.586195360374</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>584.0077733786979</v>
+        <v>1407.084550540716</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>4116</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.1955479454605181</v>
+        <v>0.4568965489213738</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.1418872141347663</v>
+        <v>0.3418572766133907</v>
       </c>
     </row>
     <row r="6">
@@ -15656,6 +16206,50 @@
       </c>
       <c r="G21" s="2" t="n">
         <v>0.7347744596523256</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>180.091457272774</v>
+      </c>
+      <c r="C22" t="n">
+        <v>180.091457272774</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4116</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.04375399836559134</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>804.8811474593635</v>
+      </c>
+      <c r="C23" t="n">
+        <v>804.8753435154925</v>
+      </c>
+      <c r="D23" t="n">
+        <v>584.0077733786979</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4116</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.1955479454605181</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.1418872141347663</v>
       </c>
     </row>
   </sheetData>
@@ -15791,7 +16385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -15827,7 +16421,6 @@
           <t>NaN means not available, never zero. A basal source a method does not resolve is NaN, and a method that raised leaves its entire block NaN.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -15840,7 +16433,6 @@
           <t>sppr_all, sppr_inner and sppr_PP are the same table under three source scopes, mirroring get_PPR: sppr_all sums every basal source, sppr_inner drops Import, and sppr_PP drops Import and Detritus. Each is a flat groups x methods table -- rows are group seq with the group name in the first column, one column per method, no MultiIndex. Sums are taken over each method's own basal-source columns before aggregation; the per-source breakdown itself is not written to the workbook.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -15853,7 +16445,6 @@
           <t>SPPR_1986 and SPPR_1995 return one un-attributed SPPR column, so their value cannot be split into a PP-only part: they are NaN in sppr_PP (and in ppr_pp_only) while sppr_inner and sppr_all carry the total. A method that resolves no Detritus source (SPPR_2015) has sppr_inner equal to sppr_PP by construction.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -15866,7 +16457,6 @@
           <t>SPPR_2015() has no only_pp_det parameter (only_pp belongs to get_PPR / get_PPR2NPP_ratio). It is called bare here and PP-only filtering is applied downstream at the get_PPR layer, which is what the ppr_pp_only column and SUM_PP already do.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -15879,7 +16469,6 @@
           <t>Under det_open_mode='none' det_theta does not affect the recycling gain b at all (verified: identical b at theta = 1, 3 and 10). Do not read the health sheet as a theta sensitivity.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -15892,7 +16481,6 @@
           <t>MC runs use exclude_diverged=True, so draws graded FAIL on divergence are dropped as well as draws with a negative SPPR. The two are often the same draws rather than additive -- see the mc_diagnostics sheet for the split by cause.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -15905,7 +16493,6 @@
           <t>SPPR_EwE and the Monte-Carlo methods are called with silent=True rather than silent=False: PPRCalculator imports tqdm.notebook, whose bar needs ipywidgets and raises ImportError('IProgress not found') outside Jupyter, which makes those methods fail outright in a terminal run. Nothing is lost -- this exporter has its own progress bar, and the MC rejection counts appear in mc_diagnostics and in the run report.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -15918,7 +16505,6 @@
           <t>diagnose_sppr grades a CONFIGURATION, not a model: a model can be healthy under one TE_option and divergent under another. Read each row with its config_ columns.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -15931,7 +16517,6 @@
           <t>Every SPPR method, and every diagnose_sppr row, runs in a worker process with a wall-clock budget (180 s by default; --timeout SECONDS on the command line, method_timeout= from Python, and None or 0 to disable it). A method still running when the budget expires is killed and left NaN, exactly like a method that raised -- the status column of this sheet and the run report are the only places that say which of the two happened. A timeout is a statement about this machine and this model, not about the method: rerun it with a larger budget before reading anything into it.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -15975,7 +16560,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'.</t>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'. Arithmetic mean with consumer consumption weights.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -15992,7 +16577,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nullspace form of the EwE path sum, global TE at the true mean (Jensen-able on TL).</t>
+          <t>Nullspace form of the EwE path sum, global TE at the consumer consumption-weighted arithmetic mean (Jensen-able on TL).</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -16268,6 +16853,40 @@
         </is>
       </c>
       <c r="C30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>method: SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'. Arithmetic mean with consumer catch weights. Consumer biomass fallback when consumer catch is zero.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>method: Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Nullspace form of the EwE path sum, global TE at the consumer catch-weighted arithmetic mean. Consumer biomass fallback when consumer catch is zero (Jensen-able on TL).</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
